--- a/outputs/forecast_311_call_volume_by_tract.xlsx
+++ b/outputs/forecast_311_call_volume_by_tract.xlsx
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>1013.162232285491</v>
+        <v>871.9402549765636</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>1189.433457260316</v>
+        <v>1020.467274103438</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>1397.918675764297</v>
+        <v>1200.171455103368</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>1410.897265403119</v>
+        <v>1205.608705264382</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>1669.244582279627</v>
+        <v>1423.467730870868</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>1975.526580689438</v>
+        <v>1685.222809457395</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>1052.228467772275</v>
+        <v>907.8192402797539</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>1231.855759762103</v>
+        <v>1059.679343211983</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>1443.495177837712</v>
+        <v>1242.526468457363</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>460.7852370830066</v>
+        <v>411.30157348697</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>516.8739619203596</v>
+        <v>460.3859196063655</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>583.9234543853001</v>
+        <v>520.5275511295555</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>445.3293668808616</v>
+        <v>404.7836972924603</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>488.6697327984384</v>
+        <v>443.4481606383673</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>541.7163673898232</v>
+        <v>491.9051556897077</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>544.5725858532984</v>
+        <v>494.9911680915399</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>597.5715271727737</v>
+        <v>542.2721580554434</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>662.4397938843382</v>
+        <v>601.5279689701368</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>2266.992317566551</v>
+        <v>1900.187488712813</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>2738.680802740593</v>
+        <v>2293.883813387159</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>3308.602648232543</v>
+        <v>2771.425256179895</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>464.5081911774571</v>
+        <v>389.3581253188617</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>561.1432129381861</v>
+        <v>470.0168207652198</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>677.9003572506962</v>
+        <v>567.8505871221131</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>841.7884055526011</v>
+        <v>724.4537757992466</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>988.2437867739764</v>
+        <v>847.8578128029973</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>1161.464247727255</v>
+        <v>997.165480017944</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>1454.278016551413</v>
+        <v>1243.860742140015</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>1718.847946895643</v>
+        <v>1466.959145468122</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>2032.322377322755</v>
+        <v>1735.14944692327</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>856.5998846526403</v>
+        <v>737.604050618747</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>1005.017774175699</v>
+        <v>862.7528051941805</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>1180.409494138758</v>
+        <v>1014.009050989033</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>829.0885552177521</v>
+        <v>753.6029507131833</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>909.7772514334342</v>
+        <v>825.5862874223799</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>1008.536431821686</v>
+        <v>915.8007461576241</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>708.1973832673657</v>
+        <v>643.7184987252957</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>777.120666746732</v>
+        <v>705.2057770099394</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>861.4795574906764</v>
+        <v>782.2658691682581</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>510.2439936351352</v>
+        <v>463.1027025910418</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>562.3094036496848</v>
+        <v>509.2972183974868</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>623.8192385145015</v>
+        <v>565.4575452664405</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>533.6080376546969</v>
+        <v>485.0249037005465</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>585.5398840350698</v>
+        <v>531.3539260002578</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>649.1020780684667</v>
+        <v>589.4166665860778</v>
       </c>
     </row>
     <row r="77">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>482.4401454039757</v>
+        <v>438.5156692063574</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>529.3922165339134</v>
+        <v>480.4021764577897</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>586.8594046642828</v>
+        <v>532.8972555340573</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>843.7974751614664</v>
+        <v>765.5176098549126</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>930.3028685944124</v>
+        <v>842.3297613256964</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>1032.430404858627</v>
+        <v>935.5102495381685</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>877.1638801839341</v>
+        <v>797.3011847048805</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>962.5313826488261</v>
+        <v>873.458536977773</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>1067.017189661193</v>
+        <v>968.9041508313179</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>638.908190232818</v>
+        <v>563.6210564793565</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>729.3929283881282</v>
+        <v>642.4074396707389</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>832.8617236846823</v>
+        <v>733.7209474352095</v>
       </c>
     </row>
     <row r="97">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>329.5677027402589</v>
+        <v>290.7323875376612</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>376.2423896371219</v>
+        <v>331.3727158699036</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>429.6146350281554</v>
+        <v>378.4749091351787</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>134.5779920869134</v>
+        <v>118.7197123878523</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>153.6374552391452</v>
+        <v>135.3150621647344</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>175.4318457135379</v>
+        <v>154.5490976798655</v>
       </c>
     </row>
     <row r="107">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>824.4585324616096</v>
+        <v>727.3066612772031</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>941.2216648055955</v>
+        <v>828.9740292337746</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>1074.739657590043</v>
+        <v>946.8066182857496</v>
       </c>
     </row>
     <row r="112">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>353.8402797880503</v>
+        <v>312.1447524334426</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>403.952546695809</v>
+        <v>355.778231986671</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>461.2556457251956</v>
+        <v>406.3494907363517</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>139.0239114652393</v>
+        <v>128.3142626059436</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>149.6195369937727</v>
+        <v>137.7429857031163</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>163.5794262904928</v>
+        <v>150.740958249835</v>
       </c>
     </row>
     <row r="122">
@@ -1946,7 +1946,7 @@
         <v>2024</v>
       </c>
       <c r="D122">
-        <v>0.1264134317175541</v>
+        <v>0.07047408825338013</v>
       </c>
     </row>
     <row r="123">
@@ -1959,7 +1959,7 @@
         <v>2025</v>
       </c>
       <c r="D123">
-        <v>0.04646376802548044</v>
+        <v>0.07042457952191798</v>
       </c>
     </row>
     <row r="124">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>0.1224510468159957</v>
+        <v>0.07042459111537287</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>0.05512119579448101</v>
+        <v>0.07037511715613091</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>0.1211129830624979</v>
+        <v>0.07032567795282584</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>14.17228180024737</v>
+        <v>13.08054250072497</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>15.25238948408151</v>
+        <v>14.04169899839689</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>16.67545532610676</v>
+        <v>15.36670887014522</v>
       </c>
     </row>
     <row r="132">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>11.13541165078989</v>
+        <v>10.27760050944226</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>11.98408542168711</v>
+        <v>11.03281043060604</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>13.10223162494748</v>
+        <v>12.07390956580816</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>5.398987646692422</v>
+        <v>4.983079289139964</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>5.810465143706378</v>
+        <v>5.349241209072122</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>6.352596599668392</v>
+        <v>5.85401646335573</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>518.6401427977809</v>
+        <v>478.6869009259868</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>558.1681199968049</v>
+        <v>513.8616121878063</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>610.2466453255622</v>
+        <v>562.3516360400494</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>543.2730181284686</v>
+        <v>501.4221916978104</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>584.6783853683818</v>
+        <v>538.2675328167235</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>639.2303868891157</v>
+        <v>589.0605967953221</v>
       </c>
     </row>
     <row r="152">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>290.1955333327189</v>
+        <v>267.8404369966616</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>312.3126539104283</v>
+        <v>287.5217777851993</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>341.4522305980006</v>
+        <v>314.6534726137159</v>
       </c>
     </row>
     <row r="157">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>527.0077657754171</v>
+        <v>486.402046924702</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>567.1876384159341</v>
+        <v>522.1556789787112</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>620.117133687771</v>
+        <v>571.4375126263741</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>192.5503357989193</v>
+        <v>171.1615999981518</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>218.0818126192723</v>
+        <v>193.334454380787</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>247.201216358795</v>
+        <v>219.2777882589955</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>734.3803152141933</v>
+        <v>647.8430115230807</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>838.3862036699547</v>
+        <v>738.4024592628648</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>957.3163590892776</v>
+        <v>843.3609593244752</v>
       </c>
     </row>
     <row r="172">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>560.9662564956859</v>
+        <v>494.8635832157671</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>640.4125417645872</v>
+        <v>564.0386231581898</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>731.2589276095239</v>
+        <v>644.2125752899324</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>532.8228710722075</v>
+        <v>470.0031888753328</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>608.3318728184761</v>
+        <v>535.7442143748698</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>694.6833909853142</v>
+        <v>611.946044958666</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>533.5457058108847</v>
+        <v>483.4161797251666</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>589.1097768195988</v>
+        <v>532.7142858181401</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>654.666575177551</v>
+        <v>592.4406859360114</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>976.9209238651692</v>
+        <v>886.0019079007556</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>1077.140536005473</v>
+        <v>975.1270432254784</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>1195.757681637572</v>
+        <v>1083.273047169405</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>845.5986058303505</v>
+        <v>772.1329525027923</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>927.1224794845733</v>
+        <v>845.255110576701</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>1020.735353085506</v>
+        <v>931.1521461334765</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>939.9720171031078</v>
+        <v>869.0941414939866</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>1012.593503973214</v>
+        <v>934.0309356339786</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>1103.268738118815</v>
+        <v>1018.611419731712</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>523.3621113244737</v>
+        <v>483.0456763880356</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>563.2493103194486</v>
+        <v>518.5400636790301</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>615.8011542704612</v>
+        <v>567.4708586381279</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>1011.635068591567</v>
+        <v>933.7041388735365</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>1088.736604252402</v>
+        <v>1002.314358927819</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>1190.318535722118</v>
+        <v>1096.896736188696</v>
       </c>
     </row>
     <row r="212">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>968.042158967089</v>
+        <v>905.9051538948916</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>1034.640442195362</v>
+        <v>965.2937295220116</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>1111.413052649932</v>
+        <v>1038.031884604128</v>
       </c>
     </row>
     <row r="217">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>1219.070308878843</v>
+        <v>1134.726249405795</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>1306.862341478497</v>
+        <v>1212.542357614179</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>1413.621064118618</v>
+        <v>1313.184571491986</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>750.0936831067098</v>
+        <v>695.7557564746498</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>807.7779330977596</v>
+        <v>747.8615368162715</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>875.4502503281332</v>
+        <v>811.1072888442009</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>1031.854814030816</v>
+        <v>960.6523296619008</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>1110.319052645752</v>
+        <v>1033.695454052958</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>1194.759564443554</v>
+        <v>1112.311143706708</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>1230.706172968368</v>
+        <v>1145.71613955559</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>1324.373464041391</v>
+        <v>1232.918914314355</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>1425.163926000787</v>
+        <v>1326.747854336849</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>612.2494255800269</v>
+        <v>577.3611503047482</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>650.6620182329051</v>
+        <v>612.5878474307602</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>691.8235277880235</v>
+        <v>651.5783238669852</v>
       </c>
     </row>
     <row r="242">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>451.5890342881355</v>
+        <v>425.8555769691918</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>479.9220315221573</v>
+        <v>451.8386566455881</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>510.2826385405061</v>
+        <v>480.5979014502663</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>592.9507824350743</v>
+        <v>559.1622185523483</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>630.1525737135929</v>
+        <v>593.2785363589531</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>670.0166337962316</v>
+        <v>631.0399966482996</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>840.9383493241454</v>
+        <v>793.0184935802469</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>893.6989388025078</v>
+        <v>841.4031860259211</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>950.2352253102295</v>
+        <v>894.9575044789609</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>544.7041747207959</v>
+        <v>513.6648887987041</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>578.8789631777431</v>
+        <v>545.0052589709585</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>615.4994001421807</v>
+        <v>579.6941793469065</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>839.6465954925263</v>
+        <v>793.6474409097</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>890.0178428718175</v>
+        <v>839.6442466852392</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>944.321475215197</v>
+        <v>891.3286378598468</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>397.6933076573334</v>
+        <v>375.0005791175017</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>422.6814125256037</v>
+        <v>397.907874921703</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>449.4667751468451</v>
+        <v>423.2804984432607</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>373.3824755944287</v>
+        <v>346.9822032279101</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>396.4031616650694</v>
+        <v>368.9912561508597</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>430.104619985697</v>
+        <v>399.9634190817317</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>10.02778848878589</v>
+        <v>9.069859476758898</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>11.14475412628321</v>
+        <v>10.05878854812133</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>12.39089292496279</v>
+        <v>11.1878118466773</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>149.6647239361672</v>
+        <v>135.3676155634875</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>166.3354570483338</v>
+        <v>150.127405104186</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>184.9341006672271</v>
+        <v>166.9780938839094</v>
       </c>
     </row>
     <row r="287">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>617.2102610460253</v>
+        <v>558.2496182355269</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>685.9596276449771</v>
+        <v>619.1183478203986</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>762.6596090878869</v>
+        <v>688.609832592963</v>
       </c>
     </row>
     <row r="292">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>615.9567869646057</v>
+        <v>557.1158852885777</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>684.5665328344382</v>
+        <v>617.8609987603373</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>761.1107468758202</v>
+        <v>687.2113555582881</v>
       </c>
     </row>
     <row r="297">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>381.3065910725508</v>
+        <v>344.8812790495485</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>423.7792814332606</v>
+        <v>382.4853864688702</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>471.1637849371778</v>
+        <v>425.4165524809964</v>
       </c>
     </row>
     <row r="302">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>532.4754683256392</v>
+        <v>481.6093444238084</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>591.7864532660715</v>
+        <v>534.12159906566</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>657.9565386983087</v>
+        <v>594.0728200966731</v>
       </c>
     </row>
     <row r="307">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>25.79575658226735</v>
+        <v>23.28718095811576</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>28.6817924326785</v>
+        <v>25.81546434363461</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>31.99394411938805</v>
+        <v>28.82383104477797</v>
       </c>
     </row>
     <row r="312">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>505.0540200903362</v>
+        <v>455.9385102997325</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>561.5600091941589</v>
+        <v>505.4400177228665</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>626.4087982482387</v>
+        <v>564.3409425109112</v>
       </c>
     </row>
     <row r="317">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>575.2012751135891</v>
+        <v>519.2638590628191</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>639.5557126846826</v>
+        <v>575.6409024915578</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>713.4117565940626</v>
+        <v>642.7229147974448</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>266.3300018139882</v>
+        <v>240.4299521794401</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>296.1272495287835</v>
+        <v>266.5335341033103</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>330.3239175170864</v>
+        <v>297.593722953286</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>704.9146897609003</v>
+        <v>647.7315205782382</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>767.7634273301609</v>
+        <v>702.6272323142916</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>841.8490173662029</v>
+        <v>771.509044819088</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>878.528356348825</v>
+        <v>815.468989137651</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>934.2162279627098</v>
+        <v>868.406376546774</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>1014.833077659503</v>
+        <v>942.5258873236793</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>703.5042020039771</v>
+        <v>653.0077906512739</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>748.0976447950012</v>
+        <v>695.3987359464817</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>812.6536697344884</v>
+        <v>754.7518388444888</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>310.087070436996</v>
+        <v>287.8295148161653</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>329.7426553755597</v>
+        <v>306.5143332201775</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>358.1973499094923</v>
+        <v>332.6756919073493</v>
       </c>
     </row>
     <row r="347">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>249.2518030360505</v>
+        <v>227.2273482758712</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>273.5049104000497</v>
+        <v>248.6773099099211</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>302.1100980361844</v>
+        <v>274.9556038240949</v>
       </c>
     </row>
     <row r="352">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>420.6526966232839</v>
+        <v>379.7449000668192</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>467.7159622632819</v>
+        <v>420.9741905790403</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>521.7278950318187</v>
+        <v>470.0321846394615</v>
       </c>
     </row>
     <row r="357">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>360.4805669934601</v>
+        <v>325.6276792647691</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>400.4962788143247</v>
+        <v>360.6966458467539</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>446.4632943612042</v>
+        <v>402.4800467229963</v>
       </c>
     </row>
     <row r="362">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>782.1876250002584</v>
+        <v>726.0434431081871</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>831.7686498422039</v>
+        <v>773.1756194550671</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>903.5449384377596</v>
+        <v>839.1670710934072</v>
       </c>
     </row>
     <row r="367">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>578.3541865635722</v>
+        <v>536.8408443314225</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>615.0146313026021</v>
+        <v>571.6906222486999</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>668.0864548591221</v>
+        <v>620.4850909084321</v>
       </c>
     </row>
     <row r="372">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>779.3996303832861</v>
+        <v>723.4555660398811</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>828.8039318535137</v>
+        <v>770.4197472315687</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>900.3243845295048</v>
+        <v>836.175982255435</v>
       </c>
     </row>
     <row r="377">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>586.2494871885367</v>
+        <v>544.7704230667631</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>622.4394651194423</v>
+        <v>579.3610375320014</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>675.3932032040383</v>
+        <v>628.0273851706725</v>
       </c>
     </row>
     <row r="382">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>477.4113937213452</v>
+        <v>417.6560689393006</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>547.8693614459279</v>
+        <v>478.2185403473132</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>632.5899732165641</v>
+        <v>552.6235761279457</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>724.8466264410283</v>
+        <v>647.0587171449029</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>816.6938856453994</v>
+        <v>727.611944803316</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>920.8673385937116</v>
+        <v>820.8026168933798</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>183.0073590050473</v>
+        <v>175.4545892565546</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>191.0244683020046</v>
+        <v>182.6284407934226</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>199.9402165198752</v>
+        <v>191.3240146089757</v>
       </c>
     </row>
     <row r="397">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>325.729831862848</v>
+        <v>289.7167279158392</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>368.457542832818</v>
+        <v>327.0736048477741</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>417.1074155707615</v>
+        <v>370.4315967554758</v>
       </c>
     </row>
     <row r="402">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>876.4991786983242</v>
+        <v>780.8182588070564</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>989.7893561800469</v>
+        <v>880.0336269662356</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>1118.518447785274</v>
+        <v>994.9356608878816</v>
       </c>
     </row>
     <row r="407">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>567.9346601398119</v>
+        <v>494.455345104469</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>656.8053055695349</v>
+        <v>570.4110529627559</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>761.9116411112267</v>
+        <v>662.2172022735244</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>662.7366428593934</v>
+        <v>576.4777782600435</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>767.0906348310957</v>
+        <v>665.5991079652134</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>890.765484837772</v>
+        <v>773.5309208427537</v>
       </c>
     </row>
     <row r="417">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>989.8545014421899</v>
+        <v>883.2560730127116</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>1115.79923898346</v>
+        <v>993.7423859794006</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>1258.61175261184</v>
+        <v>1121.421831012497</v>
       </c>
     </row>
     <row r="422">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>151.2961896250176</v>
+        <v>145.0521739872713</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>157.9240812033695</v>
+        <v>150.9829283245658</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>165.2948954494537</v>
+        <v>158.1717220926136</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>362.448795798867</v>
+        <v>347.4904046263325</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>378.3268374702905</v>
+        <v>361.6983608408341</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>395.9846252563664</v>
+        <v>378.9200861751747</v>
       </c>
     </row>
     <row r="432">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>145.8199776690577</v>
+        <v>139.8019673658559</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>152.2079689595803</v>
+        <v>145.5180546233531</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>159.3119928646275</v>
+        <v>152.4466464977552</v>
       </c>
     </row>
     <row r="437">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>235.4769694372394</v>
+        <v>225.7587945576532</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>245.7926157124401</v>
+        <v>234.989418127822</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>257.264535380307</v>
+        <v>246.1780401766622</v>
       </c>
     </row>
     <row r="442">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>766.0669170475857</v>
+        <v>730.4106870570023</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>798.294365456867</v>
+        <v>760.3468556443163</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>841.6933165590882</v>
+        <v>802.018199687847</v>
       </c>
     </row>
     <row r="447">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>1093.206889102899</v>
+        <v>1042.253377179824</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>1139.118325771544</v>
+        <v>1084.948300237834</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>1201.162623955257</v>
+        <v>1144.495946276567</v>
       </c>
     </row>
     <row r="452">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>1448.835547966405</v>
+        <v>1381.306263161098</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>1509.682652747148</v>
+        <v>1437.890440503495</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>1591.910680438222</v>
+        <v>1516.809627050591</v>
       </c>
     </row>
     <row r="457">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>912.4895845924925</v>
+        <v>869.9697716365916</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>950.8234559595114</v>
+        <v>905.6107417424059</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>1002.59435852266</v>
+        <v>955.3024663582213</v>
       </c>
     </row>
     <row r="462">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>117.6748816549196</v>
+        <v>112.8184071344864</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>122.8299253682375</v>
+        <v>117.4312310042406</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>128.5628041452356</v>
+        <v>123.0225370561309</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>438.4450576418235</v>
+        <v>391.2284871798105</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>494.2308523504428</v>
+        <v>440.1671439016072</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>557.4880431376224</v>
+        <v>496.7213177099629</v>
       </c>
     </row>
     <row r="472">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>122.641621439696</v>
+        <v>117.5801829037326</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>128.0142303482015</v>
+        <v>122.3876878650357</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>133.9890598189121</v>
+        <v>128.2149705356032</v>
       </c>
     </row>
     <row r="477">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>326.0256231196087</v>
+        <v>312.5704318689848</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>340.3080447847956</v>
+        <v>325.3505982911223</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>356.1913654567414</v>
+        <v>340.8416777870486</v>
       </c>
     </row>
     <row r="482">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>152.1462791429674</v>
+        <v>145.7506627293201</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>158.8747448880315</v>
+        <v>151.7711192701706</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>166.4506457427896</v>
+        <v>159.1572232579295</v>
       </c>
     </row>
     <row r="487">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>550.6324969906132</v>
+        <v>524.9679559112462</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>573.7573204935986</v>
+        <v>546.4727044002884</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>605.0081440645022</v>
+        <v>576.4659871829047</v>
       </c>
     </row>
     <row r="492">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>645.7176331849345</v>
+        <v>615.6211613527761</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>672.8358540635902</v>
+        <v>640.8395291407473</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>709.4832869277262</v>
+        <v>676.0122580587504</v>
       </c>
     </row>
     <row r="497">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>612.948272215652</v>
+        <v>584.3791591079829</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>638.6902683835237</v>
+        <v>608.3177205245066</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>673.4778906778802</v>
+        <v>641.705477092352</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>799.8947891815405</v>
+        <v>762.6122193934698</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>833.4880398659877</v>
+        <v>793.851974734072</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>878.8857286742267</v>
+        <v>837.4228525739182</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>339.0165336736705</v>
+        <v>322.3844257406236</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>353.5626889051852</v>
+        <v>336.1163301820133</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>373.9287869179375</v>
+        <v>355.5026698322644</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>567.115065726265</v>
+        <v>516.1220214940085</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>623.1284476980918</v>
+        <v>565.9957071874568</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>689.202535703534</v>
+        <v>626.4820163759636</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>349.8266495620471</v>
+        <v>334.736183775428</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>365.3217083800573</v>
+        <v>348.6291175559155</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>383.3141946665789</v>
+        <v>366.1541842028944</v>
       </c>
     </row>
     <row r="522">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>133.4667476824795</v>
+        <v>127.9585372871265</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>139.3135963075428</v>
+        <v>133.1904005785657</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>145.815823466682</v>
+        <v>139.5320558189015</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>620.161579280371</v>
+        <v>569.6861577848892</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>645.2404892224645</v>
+        <v>600.6977669427669</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>715.4202134466085</v>
+        <v>660.274093983148</v>
       </c>
     </row>
     <row r="532">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>877.2545851970723</v>
+        <v>819.7901241525459</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>921.3898799553664</v>
+        <v>865.0271230063371</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>994.4693345074335</v>
+        <v>931.0379332199574</v>
       </c>
     </row>
     <row r="537">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>931.2175038683945</v>
+        <v>870.2842505338696</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>978.1000135975946</v>
+        <v>918.3084838336972</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>1055.554917918087</v>
+        <v>988.2908117946919</v>
       </c>
     </row>
     <row r="542">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>1235.025098793416</v>
+        <v>1154.212502342502</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>1297.20300551515</v>
+        <v>1217.904580227769</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>1399.927392489858</v>
+        <v>1310.718498932808</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>310.7182321255319</v>
+        <v>290.2679643978097</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>326.5451938846554</v>
+        <v>306.4489878195138</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>352.5368461664598</v>
+        <v>329.9334240588823</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>846.8743238967439</v>
+        <v>791.4599800769614</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>889.5105234807636</v>
+        <v>835.1345029163504</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>959.9501057361766</v>
+        <v>898.7783177045612</v>
       </c>
     </row>
     <row r="557">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>936.1510933643493</v>
+        <v>866.3735417344573</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>1004.26986810704</v>
+        <v>930.3368984477444</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>1091.600938376401</v>
+        <v>1010.67396661593</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>574.1517379976294</v>
+        <v>534.1674789903839</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>618.2787780967366</v>
+        <v>575.2954757461604</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>665.6744472610478</v>
+        <v>619.3683211184713</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>1153.605746520873</v>
+        <v>1075.534241777848</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>1239.497084558264</v>
+        <v>1155.283611524991</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>1332.1453695175</v>
+        <v>1241.749400198879</v>
       </c>
     </row>
     <row r="572">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>689.4439984566251</v>
+        <v>650.1568781831901</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>732.6997959298434</v>
+        <v>689.8250918159041</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>779.0511027954226</v>
+        <v>733.7316323939637</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>801.1005983669935</v>
+        <v>770.305567116104</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>816.0329718675707</v>
+        <v>790.2986643683513</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>854.9918060124451</v>
+        <v>824.0417920823365</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>1442.614546916107</v>
+        <v>1387.159107889234</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>1469.504899823206</v>
+        <v>1423.162641470589</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>1539.661573994047</v>
+        <v>1483.92700691112</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>536.3890381927843</v>
+        <v>515.7697692700179</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>546.3871606755116</v>
+        <v>529.156408805758</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>572.4726443104262</v>
+        <v>551.7496143929073</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>726.9570513017394</v>
+        <v>697.4736317419432</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>746.1868480172838</v>
+        <v>718.9972103599339</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>782.3354562369203</v>
+        <v>751.8264518519812</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>448.6934258197505</v>
+        <v>423.1252007767853</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>476.8444813318295</v>
+        <v>448.9414380597102</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>507.0101107207489</v>
+        <v>477.516005957443</v>
       </c>
     </row>
     <row r="602">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>1057.935222340891</v>
+        <v>987.346024100812</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>1135.560366692109</v>
+        <v>1059.294563575179</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>1219.343860293582</v>
+        <v>1137.613149775528</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>1516.566695150809</v>
+        <v>1410.951925187327</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>1633.124253119437</v>
+        <v>1519.587766150644</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>1758.31563406259</v>
+        <v>1636.002194110945</v>
       </c>
     </row>
     <row r="612">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>719.0413119675471</v>
+        <v>670.6138818948428</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>772.3085431642835</v>
+        <v>720.0417843595129</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>829.7827690062152</v>
+        <v>773.7108747126819</v>
       </c>
     </row>
     <row r="617">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>731.170586172086</v>
+        <v>679.9942391420171</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>788.0107075346425</v>
+        <v>731.9206648830274</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>849.9157702023398</v>
+        <v>789.6990213030227</v>
       </c>
     </row>
     <row r="622">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>945.2996417377614</v>
+        <v>890.1632430988669</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>1005.510087368136</v>
+        <v>944.8914416475382</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>1071.334430503815</v>
+        <v>1007.381386536571</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>704.8418358018954</v>
+        <v>677.7470856335439</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>717.9799284252881</v>
+        <v>695.3378290435616</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>752.2575407425225</v>
+        <v>725.026434989902</v>
       </c>
     </row>
     <row r="632">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>1134.206569016573</v>
+        <v>1090.606622245663</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>1155.348109362329</v>
+        <v>1118.913131385012</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>1210.506424834729</v>
+        <v>1166.687034404544</v>
       </c>
     </row>
     <row r="637">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>521.8235993185415</v>
+        <v>501.764231527097</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>531.550230303302</v>
+        <v>514.7873671107917</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>556.9273824020538</v>
+        <v>536.7670706746325</v>
       </c>
     </row>
     <row r="642">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>952.0355327421746</v>
+        <v>914.4855410048589</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>969.8620239073665</v>
+        <v>938.6828347872624</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>1017.57772095303</v>
+        <v>979.8250925341903</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>1408.186197812403</v>
+        <v>1316.178123609763</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>1438.916016582839</v>
+        <v>1369.600581912919</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>1566.285152669433</v>
+        <v>1471.129122354892</v>
       </c>
     </row>
     <row r="652">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>1572.308189428798</v>
+        <v>1481.617163332239</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>1603.503555908469</v>
+        <v>1534.652891886709</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>1726.879493339989</v>
+        <v>1634.230412892419</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>1336.113834381974</v>
+        <v>1255.807078318443</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>1364.37484901565</v>
+        <v>1303.125759422584</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>1473.946358235339</v>
+        <v>1391.478347210988</v>
       </c>
     </row>
     <row r="662">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>703.7852372193864</v>
+        <v>663.8269317637029</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>736.1221756371419</v>
+        <v>696.6890380186329</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>785.3112810398649</v>
+        <v>741.7395646321311</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>1146.2754457959</v>
+        <v>1036.682852182574</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>1272.15293707085</v>
+        <v>1147.928401586544</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>1415.132536554463</v>
+        <v>1277.853639807071</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>719.570577008131</v>
+        <v>650.7742135892489</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>798.5897080986317</v>
+        <v>720.6081977207303</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>888.3446449806014</v>
+        <v>802.1683100291212</v>
       </c>
     </row>
     <row r="677">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>1365.840038048134</v>
+        <v>1252.750089009992</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>1492.188884038233</v>
+        <v>1365.839065310707</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>1635.116236490415</v>
+        <v>1497.715052858927</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>2901.699500453697</v>
+        <v>2374.887653135033</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>3600.621308574578</v>
+        <v>2946.922342270468</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>4467.889865130354</v>
+        <v>3656.73689138621</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>1655.847418751126</v>
+        <v>1437.54262115375</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>1921.965568357095</v>
+        <v>1668.025815408106</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>2230.918161776597</v>
+        <v>1936.243716294939</v>
       </c>
     </row>
     <row r="692">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>545.0022731764839</v>
+        <v>502.5761819024987</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>586.0067299745094</v>
+        <v>540.9099159089212</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>639.8627752790329</v>
+        <v>590.2905928100087</v>
       </c>
     </row>
     <row r="697">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>1153.552474905309</v>
+        <v>1078.415064330238</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>1178.548371610675</v>
+        <v>1122.055373018922</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>1282.57798983317</v>
+        <v>1204.892945449718</v>
       </c>
     </row>
     <row r="702">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>745.3337914321362</v>
+        <v>696.7859455816052</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>761.4839478473574</v>
+        <v>724.9827600597949</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>828.6997283473902</v>
+        <v>778.5058225422945</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>866.6282756527962</v>
+        <v>810.1798409614509</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>885.4067630027971</v>
+        <v>842.9653925108319</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>963.5610876970374</v>
+        <v>905.1987087842102</v>
       </c>
     </row>
     <row r="712">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>1216.290988809233</v>
+        <v>1137.067072556579</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>1242.646378632192</v>
+        <v>1183.080868639345</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>1352.333851020191</v>
+        <v>1270.423739487205</v>
       </c>
     </row>
     <row r="717">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>1100.015603845006</v>
+        <v>1028.365346622154</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>1123.851397190999</v>
+        <v>1069.980277347933</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>1223.052977680593</v>
+        <v>1148.973326238866</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>965.3368980772195</v>
+        <v>902.4590178514321</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>986.2543206714696</v>
+        <v>938.9788605899903</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>1073.310352571359</v>
+        <v>1008.300523773349</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>1546.292168233373</v>
+        <v>1445.110719234099</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>1580.160183332156</v>
+        <v>1503.855098916851</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>1720.215535077551</v>
+        <v>1615.55596221436</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>1352.93370177746</v>
+        <v>1264.614124729883</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>1382.395368269291</v>
+        <v>1315.898301858447</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>1504.66430971219</v>
+        <v>1413.331126586314</v>
       </c>
     </row>
     <row r="737">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>1260.675364877469</v>
+        <v>1179.845195416629</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>1272.572692664865</v>
+        <v>1219.16073830992</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>1389.203052145724</v>
+        <v>1307.483703229353</v>
       </c>
     </row>
     <row r="742">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>949.0277204782408</v>
+        <v>887.5483925935388</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>965.9701064733702</v>
+        <v>921.4943986376599</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>1052.173510011335</v>
+        <v>989.0571123209821</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>1132.486434109928</v>
+        <v>1057.517959022622</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>1160.450187353566</v>
+        <v>1102.398325559901</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>1263.444533859866</v>
+        <v>1185.460385107786</v>
       </c>
     </row>
     <row r="752">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>1075.505088817298</v>
+        <v>1009.774252219381</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>1069.832811909735</v>
+        <v>1033.821628391459</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>1169.481615533108</v>
+        <v>1104.93983875338</v>
       </c>
     </row>
     <row r="757">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>1180.726859238383</v>
+        <v>1075.813053015016</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>1297.738103258594</v>
+        <v>1181.30672351209</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>1431.094106865384</v>
+        <v>1303.18635645412</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>1362.642660193458</v>
+        <v>1282.245770498992</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>1437.389392551783</v>
+        <v>1352.669355989707</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>1536.012176293569</v>
+        <v>1445.34807634627</v>
       </c>
     </row>
     <row r="767">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>1531.917147838082</v>
+        <v>1407.67807307893</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>1593.31167152375</v>
+        <v>1489.641476729191</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>1764.848156488871</v>
+        <v>1630.025658616901</v>
       </c>
     </row>
     <row r="772">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>941.7057837815687</v>
+        <v>882.3633534669843</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>938.3198663006583</v>
+        <v>905.0394435051521</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>1027.982962008795</v>
+        <v>969.3362040303408</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>995.7691064139492</v>
+        <v>935.1656833354999</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>989.4678765090434</v>
+        <v>956.7794810320343</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>1081.683566992281</v>
+        <v>1022.306849971758</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>1165.015838103744</v>
+        <v>1094.111927635741</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>1157.643732813322</v>
+        <v>1119.399374678784</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>1265.532852318209</v>
+        <v>1196.064141078425</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>1084.130853707665</v>
+        <v>1018.149666096304</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>1077.270531480481</v>
+        <v>1041.681433003251</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>1177.669137072518</v>
+        <v>1113.023507420221</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>1290.761401165449</v>
+        <v>1212.204519153226</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>1282.593671774832</v>
+        <v>1240.221386721084</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>1402.127704244379</v>
+        <v>1325.16092572822</v>
       </c>
     </row>
     <row r="797">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>223.6232861256731</v>
+        <v>210.0133248848447</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>222.2079871239294</v>
+        <v>214.8671346685618</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>242.9173368134346</v>
+        <v>229.5828700210124</v>
       </c>
     </row>
     <row r="802">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>1504.869042534759</v>
+        <v>1413.281315773874</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>1495.346679773027</v>
+        <v>1445.945662800526</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>1634.708686000041</v>
+        <v>1544.974802769276</v>
       </c>
     </row>
     <row r="807">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>454.0435800267966</v>
+        <v>426.4100256505653</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>451.1701684749831</v>
+        <v>436.2652490487296</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>493.2181749078402</v>
+        <v>466.1439744698733</v>
       </c>
     </row>
     <row r="812">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>789.9808016990044</v>
+        <v>735.9874516632875</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>795.2764659845188</v>
+        <v>760.9279740575724</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>874.6691303227982</v>
+        <v>819.9754660021071</v>
       </c>
     </row>
     <row r="817">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>1900.354129144319</v>
+        <v>1762.512364245481</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>1934.354681175133</v>
+        <v>1836.394174710969</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>2131.660519655322</v>
+        <v>1988.789776658258</v>
       </c>
     </row>
     <row r="822">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>737.4679748106098</v>
+        <v>677.6590190736125</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>767.0232183084913</v>
+        <v>717.1162775840018</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>849.6013122822778</v>
+        <v>784.6975018004596</v>
       </c>
     </row>
     <row r="827">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>780.8429491907136</v>
+        <v>705.9532688941117</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>859.5558285457131</v>
+        <v>778.2196700415271</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>957.06444154696</v>
+        <v>865.8210730944623</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>886.5935694059602</v>
+        <v>852.5121070207032</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>903.1195442003768</v>
+        <v>874.6388708834648</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>946.2360394249239</v>
+        <v>911.9830510104202</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>860.6290519788204</v>
+        <v>827.5456862130623</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>876.6710472830846</v>
+        <v>849.0244512806445</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>918.5248515180075</v>
+        <v>885.2749835933042</v>
       </c>
     </row>
     <row r="842">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>567.2837375922983</v>
+        <v>527.0013037206069</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>602.2458617761364</v>
+        <v>560.4693323103847</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>653.7481226821394</v>
+        <v>607.7592406835247</v>
       </c>
     </row>
     <row r="847">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>385.9825026167003</v>
+        <v>358.2772937409231</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>410.448924274732</v>
+        <v>381.5353357919542</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>445.8680500615692</v>
+        <v>414.0998256510005</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>717.9146508624013</v>
+        <v>665.8093334185172</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>757.0461104846252</v>
+        <v>704.7886481185036</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>825.6456159830755</v>
+        <v>766.8687924433674</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>606.8071969982974</v>
+        <v>563.9933299923582</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>637.1614549830265</v>
+        <v>595.117667620647</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>693.5211510559838</v>
+        <v>645.8299343457693</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>885.1006317989415</v>
+        <v>796.0395053752701</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>977.6916399846056</v>
+        <v>880.171430189322</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>1096.239446491502</v>
+        <v>986.343906091683</v>
       </c>
     </row>
     <row r="867">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>185.7750677503328</v>
+        <v>167.7087586946156</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>206.5598302326335</v>
+        <v>185.9170369766293</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>230.4133813394155</v>
+        <v>207.5827597741273</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>900.610475076519</v>
+        <v>809.8011894575817</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>995.1357450083375</v>
+        <v>895.659523709763</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>1116.049940116756</v>
+        <v>1003.932053400537</v>
       </c>
     </row>
     <row r="877">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>457.9880519700893</v>
+        <v>413.4496197610049</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>509.2282396136406</v>
+        <v>458.3380745701058</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>568.0337653735673</v>
+        <v>511.7500189857657</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>292.0609042507642</v>
+        <v>263.6869014853401</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>324.6252161494149</v>
+        <v>292.2198062190692</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>362.0923862388402</v>
+        <v>326.2595022130064</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>1016.15924768884</v>
+        <v>913.6990813872591</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>1122.812178890141</v>
+        <v>1010.573096215622</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>1259.239730745987</v>
+        <v>1132.737052441656</v>
       </c>
     </row>
     <row r="892">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>885.9477821824281</v>
+        <v>797.4047367125427</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>977.6229109525082</v>
+        <v>880.8044465692516</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>1095.357316190232</v>
+        <v>986.3093364417228</v>
       </c>
     </row>
     <row r="897">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>1064.214748878794</v>
+        <v>986.9754308277156</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>1122.222159224512</v>
+        <v>1044.757242042322</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>1223.911928996895</v>
+        <v>1136.782945700067</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>1645.938123356339</v>
+        <v>1526.478104364586</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>1735.653895161613</v>
+        <v>1615.844848356891</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>1892.9294747569</v>
+        <v>1758.173831091617</v>
       </c>
     </row>
     <row r="907">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>486.5416195130713</v>
+        <v>451.2290518246378</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>513.0615430834714</v>
+        <v>477.645893405077</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>559.5524845282553</v>
+        <v>519.7185490415993</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>778.1627694442366</v>
+        <v>721.6847231928795</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>820.5781987870826</v>
+        <v>763.9352304317691</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>894.9346378894035</v>
+        <v>831.2252020402408</v>
       </c>
     </row>
     <row r="917">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>1494.409004480018</v>
+        <v>1411.719241131909</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>1533.834087727374</v>
+        <v>1463.048383098801</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>1642.607466344401</v>
+        <v>1556.950186183931</v>
       </c>
     </row>
     <row r="922">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>518.943970141336</v>
+        <v>481.2796824333453</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>547.2300591051758</v>
+        <v>509.4558192221045</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>596.817167545593</v>
+        <v>554.3303989307016</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>921.9658979216684</v>
+        <v>855.0673934115388</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>972.129710076302</v>
+        <v>905.0768881586064</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>1060.209521171341</v>
+        <v>984.7683763897707</v>
       </c>
     </row>
     <row r="932">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>820.4624760829993</v>
+        <v>761.1517854836175</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>864.0925550862663</v>
+        <v>805.0465699421093</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>942.2597419947334</v>
+        <v>875.6049243879997</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>660.1979657488479</v>
+        <v>612.2816490311637</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>696.1834380897585</v>
+        <v>648.1272165319389</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>759.2678978363982</v>
+        <v>705.2164338916682</v>
       </c>
     </row>
     <row r="942">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>1102.732394127907</v>
+        <v>949.5383430236657</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>1290.966656473497</v>
+        <v>1107.3584191064</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>1518.429786256582</v>
+        <v>1304.042945619329</v>
       </c>
     </row>
     <row r="947">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>1511.734071165733</v>
+        <v>1404.828225282374</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>1527.03999381594</v>
+        <v>1455.406220224645</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>1682.617054973501</v>
+        <v>1573.797039985058</v>
       </c>
     </row>
     <row r="952">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>949.6926164421203</v>
+        <v>831.4487706157242</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>1082.844059398156</v>
+        <v>946.6157896168537</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>1251.547009516504</v>
+        <v>1094.694561785594</v>
       </c>
     </row>
     <row r="957">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>725.0714171337751</v>
+        <v>624.1013904480828</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>849.2767217433665</v>
+        <v>728.2057736543193</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>999.3216782640648</v>
+        <v>857.8899390470688</v>
       </c>
     </row>
     <row r="962">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>1125.083348375443</v>
+        <v>1017.295520229441</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>1238.292326057407</v>
+        <v>1121.261412517438</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>1378.610314570409</v>
+        <v>1247.328663001086</v>
       </c>
     </row>
     <row r="967">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>637.6362571428801</v>
+        <v>595.8835725338985</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>669.784060320302</v>
+        <v>628.8064882117877</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>722.8567885947436</v>
+        <v>676.7590353526419</v>
       </c>
     </row>
     <row r="972">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>1088.20897152233</v>
+        <v>983.8401842177769</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>1197.905975549221</v>
+        <v>1084.553121621549</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>1333.797266799774</v>
+        <v>1206.637404623775</v>
       </c>
     </row>
     <row r="977">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>56.64277619657312</v>
+        <v>52.73521727413902</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>59.79981507444302</v>
+        <v>55.91708176852296</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>64.7655249383147</v>
+        <v>60.40270540311028</v>
       </c>
     </row>
     <row r="982">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>523.188992995725</v>
+        <v>473.0105930394657</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>575.9290107675326</v>
+        <v>521.4312921026539</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>641.2627965962066</v>
+        <v>580.1269334531547</v>
       </c>
     </row>
     <row r="987">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>792.9678478418226</v>
+        <v>716.9152814694521</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>872.9029833340888</v>
+        <v>790.3038361997495</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>971.9257092516239</v>
+        <v>879.2655134758451</v>
       </c>
     </row>
     <row r="992">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>1266.444910581369</v>
+        <v>1144.981722588301</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>1394.109059573141</v>
+        <v>1262.190297606429</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>1552.257771846146</v>
+        <v>1404.270580666885</v>
       </c>
     </row>
     <row r="997">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>1283.636292412838</v>
+        <v>1115.522056382502</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>1487.768484981558</v>
+        <v>1290.463087413479</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>1728.124953296072</v>
+        <v>1499.843243563489</v>
       </c>
     </row>
     <row r="1002">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>534.3236905134914</v>
+        <v>464.3448455711939</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>619.2952621601802</v>
+        <v>537.1653787000629</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>719.3454822882223</v>
+        <v>624.3214783206314</v>
       </c>
     </row>
     <row r="1007">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>1640.628388669605</v>
+        <v>1426.159532600434</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>1900.871145536699</v>
+        <v>1649.240946733062</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>2207.309223424396</v>
+        <v>1916.2695858769</v>
       </c>
     </row>
     <row r="1012">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>696.3579691584124</v>
+        <v>632.5911975719662</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>747.1506735666194</v>
+        <v>682.4913995333177</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>833.8305521994686</v>
+        <v>759.1130649748335</v>
       </c>
     </row>
     <row r="1017">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>469.6930182499804</v>
+        <v>410.1722462648665</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>504.0461223501764</v>
+        <v>450.1458096135463</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>594.0728080488229</v>
+        <v>522.6039828829933</v>
       </c>
     </row>
     <row r="1022">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>540.9548866847109</v>
+        <v>494.7084670600482</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>575.4289417264745</v>
+        <v>528.3956873707483</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>638.823780415291</v>
+        <v>585.0692029421588</v>
       </c>
     </row>
     <row r="1027">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>629.9194527509172</v>
+        <v>545.9759131556411</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>684.4308072130937</v>
+        <v>605.2387266873149</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>812.3827106297385</v>
+        <v>708.9109901979165</v>
       </c>
     </row>
     <row r="1032">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>4.078234211812846</v>
+        <v>3.830027568976325</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>4.052412297137636</v>
+        <v>3.91854221813051</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>4.430095939935684</v>
+        <v>4.186914149628721</v>
       </c>
     </row>
     <row r="1037">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>422.0020640590967</v>
+        <v>369.3565732487307</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>457.0084991266928</v>
+        <v>406.7415126144782</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>535.6330145564384</v>
+        <v>471.5478592474093</v>
       </c>
     </row>
     <row r="1042">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>431.1088773360926</v>
+        <v>394.2216142640739</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>458.7124756252085</v>
+        <v>421.1445239742469</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>509.2755478579439</v>
+        <v>466.365633606415</v>
       </c>
     </row>
     <row r="1047">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>658.3285712924799</v>
+        <v>601.9995630470634</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>700.4809567555034</v>
+        <v>643.1124621810583</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>777.6937128135106</v>
+        <v>712.1677469538313</v>
       </c>
     </row>
     <row r="1052">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>788.3755476253187</v>
+        <v>715.2925068299654</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>854.4037442179487</v>
+        <v>776.1466204394914</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>953.5478065772462</v>
+        <v>865.4423661401712</v>
       </c>
     </row>
     <row r="1057">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>954.4286782837531</v>
+        <v>859.4664901588544</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>1050.378789896565</v>
+        <v>945.3147345448057</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>1179.141396807372</v>
+        <v>1061.31628832923</v>
       </c>
     </row>
     <row r="1062">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>444.6338596481284</v>
+        <v>406.5893496887549</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>473.1034564245414</v>
+        <v>434.3569012709415</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>525.2528197128905</v>
+        <v>480.9967119285201</v>
       </c>
     </row>
     <row r="1067">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>899.9641336706715</v>
+        <v>806.2417604456663</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>966.3557035792433</v>
+        <v>873.876901129507</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>1099.852401256185</v>
+        <v>988.7240795020334</v>
       </c>
     </row>
     <row r="1072">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>1751.498068048791</v>
+        <v>1518.092253655708</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>1903.068218789781</v>
+        <v>1682.873456456696</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>2258.839526661197</v>
+        <v>1971.13527116659</v>
       </c>
     </row>
     <row r="1077">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>675.3863082831569</v>
+        <v>611.0188920406504</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>736.4566349884199</v>
+        <v>666.5562080920168</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>823.6796649474555</v>
+        <v>745.1742027396775</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>532.5462427549454</v>
+        <v>486.979628579059</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>566.6448323205007</v>
+        <v>520.2373535650108</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>629.1050862013011</v>
+        <v>576.0987204255824</v>
       </c>
     </row>
     <row r="1087">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>590.7036641884616</v>
+        <v>540.1608891084703</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>628.5260509172726</v>
+        <v>577.0505758947326</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>697.8073546592656</v>
+        <v>639.0123565883333</v>
       </c>
     </row>
     <row r="1092">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>1005.723747125025</v>
+        <v>902.145522392264</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>1114.729809933804</v>
+        <v>998.710699276923</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>1255.513575784998</v>
+        <v>1125.322377614609</v>
       </c>
     </row>
     <row r="1097">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>1086.554847337519</v>
+        <v>961.6151206917804</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>1230.153613452821</v>
+        <v>1086.313636402852</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>1402.872345863464</v>
+        <v>1239.860268884602</v>
       </c>
     </row>
     <row r="1102">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>369.9083322818331</v>
+        <v>338.2576113806904</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>393.5932881714762</v>
+        <v>361.3585170322572</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>436.9783932618852</v>
+        <v>400.1600045717315</v>
       </c>
     </row>
     <row r="1107">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>670.8391791758874</v>
+        <v>613.4397177703189</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>713.7926144521626</v>
+        <v>655.3339112236409</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>792.4726892219904</v>
+        <v>725.701494283347</v>
       </c>
     </row>
     <row r="1112">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>1217.317424163657</v>
+        <v>1091.44371575237</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>1306.688557944757</v>
+        <v>1182.331579939171</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>1485.691095646213</v>
+        <v>1336.565692584875</v>
       </c>
     </row>
     <row r="1117">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>702.6475508163146</v>
+        <v>642.4298723851938</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>747.917469896681</v>
+        <v>686.5183798895843</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>830.4346682894505</v>
+        <v>760.3332296674821</v>
       </c>
     </row>
     <row r="1122">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>510.4860156718419</v>
+        <v>443.6291241209958</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>591.6667649043856</v>
+        <v>513.2009272514225</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>687.2534623820389</v>
+        <v>596.4687476527555</v>
       </c>
     </row>
     <row r="1127">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>1301.101204991208</v>
+        <v>1199.288950732307</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>1305.079955078559</v>
+        <v>1242.110876281618</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>1458.625907365172</v>
+        <v>1354.93568914498</v>
       </c>
     </row>
     <row r="1132">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>879.1512885522818</v>
+        <v>783.1500166054111</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>919.484064722359</v>
+        <v>840.708222920032</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>1062.080327891252</v>
+        <v>953.5718937219643</v>
       </c>
     </row>
     <row r="1137">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>1481.89479627119</v>
+        <v>1279.516701470826</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>1728.091843579943</v>
+        <v>1486.472525123037</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>2026.832546372638</v>
+        <v>1745.606395407924</v>
       </c>
     </row>
     <row r="1142">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>1413.98507269778</v>
+        <v>1217.080874962034</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>1656.20084852072</v>
+        <v>1420.097456740105</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>1948.806881467018</v>
+        <v>1672.997600895173</v>
       </c>
     </row>
     <row r="1147">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>505.6680324843891</v>
+        <v>435.251094971379</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>592.2893289298424</v>
+        <v>507.8539258828259</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>696.9313370620692</v>
+        <v>598.2962328254335</v>
       </c>
     </row>
     <row r="1152">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>1568.598309170004</v>
+        <v>1359.565827162823</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>1704.340714314475</v>
+        <v>1507.139765194022</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>2022.960727333425</v>
+        <v>1765.299916939301</v>
       </c>
     </row>
     <row r="1157">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>656.7244877670523</v>
+        <v>565.2721489552561</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>769.2218748095689</v>
+        <v>659.563382318975</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>905.1232098163273</v>
+        <v>777.0231907976495</v>
       </c>
     </row>
     <row r="1162">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>1253.630876749475</v>
+        <v>1086.547568739004</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>1362.461444112139</v>
+        <v>1204.679131069928</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>1617.094317676857</v>
+        <v>1411.062212846157</v>
       </c>
     </row>
     <row r="1167">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>1848.217938497813</v>
+        <v>1601.923176373983</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>2008.158018692023</v>
+        <v>1775.80381514183</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>2383.575432791606</v>
+        <v>2079.98379666048</v>
       </c>
     </row>
     <row r="1172">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>646.6594341863547</v>
+        <v>560.4851133872357</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>702.6194235468304</v>
+        <v>621.3228268151657</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>833.9716190764869</v>
+        <v>727.7501589365575</v>
       </c>
     </row>
     <row r="1177">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>1168.078819867787</v>
+        <v>1012.419812721225</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>1269.161174586327</v>
+        <v>1122.312768313031</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>1506.426128640276</v>
+        <v>1314.555374364797</v>
       </c>
     </row>
     <row r="1182">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>949.558882212785</v>
+        <v>883.4309915016923</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>1022.538306781363</v>
+        <v>951.4504481673872</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>1100.923559538389</v>
+        <v>1024.340249510846</v>
       </c>
     </row>
     <row r="1187">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>276.6311236915867</v>
+        <v>256.7749828143232</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>294.1660159014388</v>
+        <v>273.4438509658443</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>319.5506746760903</v>
+        <v>296.7826047563719</v>
       </c>
     </row>
     <row r="1192">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>145.8459100408253</v>
+        <v>135.3742005780031</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>155.1103026080206</v>
+        <v>144.1742551871017</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>168.4960850058338</v>
+        <v>156.4840992182266</v>
       </c>
     </row>
     <row r="1197">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>995.973748401806</v>
+        <v>949.5520638960884</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>1037.801802037733</v>
+        <v>988.4496872757517</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>1094.327864564431</v>
+        <v>1042.701138334656</v>
       </c>
     </row>
     <row r="1202">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>0.4303221502790554</v>
+        <v>0.4021644931906247</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>0.4519861230360174</v>
+        <v>0.424356416596625</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>0.4877786800899375</v>
+        <v>0.4566956511350034</v>
       </c>
     </row>
     <row r="1207">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>1014.82516141383</v>
+        <v>937.2024984566888</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>1083.71915237491</v>
+        <v>1004.45778847213</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>1182.52097740198</v>
+        <v>1093.688430396907</v>
       </c>
     </row>
     <row r="1212">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>1039.599228748237</v>
+        <v>940.2056941238328</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>1153.762126832205</v>
+        <v>1041.098349462318</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>1283.435558723844</v>
+        <v>1158.932304768095</v>
       </c>
     </row>
     <row r="1217">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>1018.933374892278</v>
+        <v>917.5298839527183</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>1133.994026255345</v>
+        <v>1019.536026157568</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>1267.327476908808</v>
+        <v>1140.084959352144</v>
       </c>
     </row>
     <row r="1222">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>3294.822841320739</v>
+        <v>2751.102335051729</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>3994.99522849549</v>
+        <v>3335.727413188311</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>4843.95904172248</v>
+        <v>4044.592370512903</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/forecast_311_call_volume_by_tract.xlsx
+++ b/outputs/forecast_311_call_volume_by_tract.xlsx
@@ -386,7 +386,7 @@
         <v>2024</v>
       </c>
       <c r="D2">
-        <v>743.8523998796909</v>
+        <v>743.8523998796907</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>871.9402549765636</v>
+        <v>1013.162232285491</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>1020.467274103438</v>
+        <v>1189.433457260316</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>1200.171455103368</v>
+        <v>1397.918675764297</v>
       </c>
     </row>
     <row r="7">
@@ -451,7 +451,7 @@
         <v>2024</v>
       </c>
       <c r="D7">
-        <v>1015.667505460171</v>
+        <v>1015.667505460262</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>2025</v>
       </c>
       <c r="D8">
-        <v>1190.261344929856</v>
+        <v>1190.261344930047</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>1205.608705264382</v>
+        <v>1410.89726540345</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>1423.467730870868</v>
+        <v>1669.24458228014</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>1685.222809457395</v>
+        <v>1975.526580690191</v>
       </c>
     </row>
     <row r="12">
@@ -516,7 +516,7 @@
         <v>2024</v>
       </c>
       <c r="D12">
-        <v>776.2754509654156</v>
+        <v>776.2754509654158</v>
       </c>
     </row>
     <row r="13">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>907.8192402797539</v>
+        <v>1052.228467772275</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>1059.679343211983</v>
+        <v>1231.855759762103</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>1242.526468457363</v>
+        <v>1443.495177837713</v>
       </c>
     </row>
     <row r="17">
@@ -581,7 +581,7 @@
         <v>2024</v>
       </c>
       <c r="D17">
-        <v>369.6209235621731</v>
+        <v>369.620923562173</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>411.30157348697</v>
+        <v>460.7852370830066</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>460.3859196063655</v>
+        <v>516.8739619203596</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>520.5275511295555</v>
+        <v>583.9234543853001</v>
       </c>
     </row>
     <row r="22">
@@ -646,7 +646,7 @@
         <v>2024</v>
       </c>
       <c r="D22">
-        <v>372.6763427607175</v>
+        <v>372.6763423930747</v>
       </c>
     </row>
     <row r="23">
@@ -659,7 +659,7 @@
         <v>2025</v>
       </c>
       <c r="D23">
-        <v>396.3453822358018</v>
+        <v>396.3453822802852</v>
       </c>
     </row>
     <row r="24">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>404.7836972924603</v>
+        <v>445.3293667020662</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>443.4481606383673</v>
+        <v>488.6697328407615</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>491.9051556897077</v>
+        <v>541.7163673957783</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>494.9911680915399</v>
+        <v>544.5725858532984</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>542.2721580554434</v>
+        <v>597.5715271727737</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>601.5279689701368</v>
+        <v>662.4397938843383</v>
       </c>
     </row>
     <row r="32">
@@ -776,7 +776,7 @@
         <v>2024</v>
       </c>
       <c r="D32">
-        <v>1557.591828717556</v>
+        <v>1557.59182871728</v>
       </c>
     </row>
     <row r="33">
@@ -789,7 +789,7 @@
         <v>2025</v>
       </c>
       <c r="D33">
-        <v>1875.978319854333</v>
+        <v>1875.978319853953</v>
       </c>
     </row>
     <row r="34">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>1900.187488712813</v>
+        <v>2266.992317565975</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>2293.883813387159</v>
+        <v>2738.680802739763</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>2771.425256179895</v>
+        <v>3308.60264823138</v>
       </c>
     </row>
     <row r="37">
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="D37">
-        <v>319.1671265991118</v>
+        <v>319.1671265990777</v>
       </c>
     </row>
     <row r="38">
@@ -854,7 +854,7 @@
         <v>2025</v>
       </c>
       <c r="D38">
-        <v>384.3990581800162</v>
+        <v>384.3990581799636</v>
       </c>
     </row>
     <row r="39">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>389.3581253188617</v>
+        <v>464.5081911773729</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>470.0168207652198</v>
+        <v>561.1432129380605</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>567.8505871221131</v>
+        <v>677.9003572505156</v>
       </c>
     </row>
     <row r="42">
@@ -906,7 +906,7 @@
         <v>2024</v>
       </c>
       <c r="D42">
-        <v>618.0316757627243</v>
+        <v>618.0316757628232</v>
       </c>
     </row>
     <row r="43">
@@ -919,7 +919,7 @@
         <v>2025</v>
       </c>
       <c r="D43">
-        <v>713.5412460824145</v>
+        <v>713.5412460824652</v>
       </c>
     </row>
     <row r="44">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>724.4537757992466</v>
+        <v>841.7884055526744</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>847.8578128029973</v>
+        <v>988.2437867740448</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>997.165480017944</v>
+        <v>1161.464247727326</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>1243.860742140015</v>
+        <v>1454.278016551413</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>1466.959145468122</v>
+        <v>1718.847946895643</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>1735.14944692327</v>
+        <v>2032.322377322755</v>
       </c>
     </row>
     <row r="52">
@@ -1036,7 +1036,7 @@
         <v>2024</v>
       </c>
       <c r="D52">
-        <v>629.5715104493986</v>
+        <v>629.5715104493984</v>
       </c>
     </row>
     <row r="53">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>737.604050618747</v>
+        <v>856.5998846526403</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>862.7528051941805</v>
+        <v>1005.017774175699</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>1014.009050989033</v>
+        <v>1180.409494138758</v>
       </c>
     </row>
     <row r="57">
@@ -1101,7 +1101,7 @@
         <v>2024</v>
       </c>
       <c r="D57">
-        <v>693.8272413058444</v>
+        <v>693.8272413058442</v>
       </c>
     </row>
     <row r="58">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>753.6029507131833</v>
+        <v>829.0885552177521</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>825.5862874223799</v>
+        <v>909.7772514334342</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>915.8007461576241</v>
+        <v>1008.536431821687</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>643.7184987252957</v>
+        <v>708.1973832673657</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>705.2057770099394</v>
+        <v>777.120666746732</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>782.2658691682581</v>
+        <v>861.4795574906765</v>
       </c>
     </row>
     <row r="67">
@@ -1231,7 +1231,7 @@
         <v>2024</v>
       </c>
       <c r="D67">
-        <v>423.7258562303499</v>
+        <v>423.72585623035</v>
       </c>
     </row>
     <row r="68">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>463.1027025910418</v>
+        <v>510.2439936351352</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>509.2972183974868</v>
+        <v>562.3094036496848</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>565.4575452664405</v>
+        <v>623.8192385145014</v>
       </c>
     </row>
     <row r="72">
@@ -1296,7 +1296,7 @@
         <v>2024</v>
       </c>
       <c r="D72">
-        <v>446.5528171359359</v>
+        <v>446.5528171358831</v>
       </c>
     </row>
     <row r="73">
@@ -1309,7 +1309,7 @@
         <v>2025</v>
       </c>
       <c r="D73">
-        <v>474.9138563110068</v>
+        <v>474.9138563109334</v>
       </c>
     </row>
     <row r="74">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>485.0249037005465</v>
+        <v>533.608037654569</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>531.3539260002578</v>
+        <v>585.5398840348955</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>589.4166665860778</v>
+        <v>649.1020780682268</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>403.7326947796162</v>
+        <v>403.7326946983937</v>
       </c>
     </row>
     <row r="78">
@@ -1374,7 +1374,7 @@
         <v>2025</v>
       </c>
       <c r="D78">
-        <v>429.3741674354801</v>
+        <v>429.3741674356766</v>
       </c>
     </row>
     <row r="79">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>438.5156692063574</v>
+        <v>482.4401453521486</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>480.4021764577897</v>
+        <v>529.3922165214852</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>532.8972555340573</v>
+        <v>586.8594046365082</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>765.5176098549126</v>
+        <v>843.7974751614664</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>842.3297613256964</v>
+        <v>930.3028685944124</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>935.5102495381685</v>
+        <v>1032.430404858627</v>
       </c>
     </row>
     <row r="87">
@@ -1491,7 +1491,7 @@
         <v>2024</v>
       </c>
       <c r="D87">
-        <v>734.0593258301487</v>
+        <v>734.0593258301486</v>
       </c>
     </row>
     <row r="88">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>797.3011847048805</v>
+        <v>877.1638801839341</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>873.458536977773</v>
+        <v>962.5313826488261</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>968.9041508313179</v>
+        <v>1067.017189661194</v>
       </c>
     </row>
     <row r="92">
@@ -1556,7 +1556,7 @@
         <v>2024</v>
       </c>
       <c r="D92">
-        <v>493.0337788139809</v>
+        <v>493.0337788139807</v>
       </c>
     </row>
     <row r="93">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>563.6210564793565</v>
+        <v>638.908190232818</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>642.4074396707389</v>
+        <v>729.3929283881282</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>733.7209474352095</v>
+        <v>832.8617236846824</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>254.3214046403946</v>
+        <v>254.3214046403977</v>
       </c>
     </row>
     <row r="98">
@@ -1634,7 +1634,7 @@
         <v>2025</v>
       </c>
       <c r="D98">
-        <v>288.3080552323299</v>
+        <v>288.308055232325</v>
       </c>
     </row>
     <row r="99">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>290.7323875376612</v>
+        <v>329.5677027402475</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>331.3727158699036</v>
+        <v>376.2423896371012</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>378.4749091351787</v>
+        <v>429.6146350281234</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>118.7197123878523</v>
+        <v>134.5779920869134</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>135.3150621647344</v>
+        <v>153.6374552391452</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>154.5490976798655</v>
+        <v>175.4318457135379</v>
       </c>
     </row>
     <row r="107">
@@ -1751,7 +1751,7 @@
         <v>2024</v>
       </c>
       <c r="D107">
-        <v>636.2195609358813</v>
+        <v>636.2195609361028</v>
       </c>
     </row>
     <row r="108">
@@ -1764,7 +1764,7 @@
         <v>2025</v>
       </c>
       <c r="D108">
-        <v>721.2418904341185</v>
+        <v>721.2418904342888</v>
       </c>
     </row>
     <row r="109">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>727.3066612772031</v>
+        <v>824.4585324618249</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>828.9740292337746</v>
+        <v>941.2216648058337</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>946.8066182857496</v>
+        <v>1074.739657590315</v>
       </c>
     </row>
     <row r="112">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>273.0521080361239</v>
+        <v>273.0521080362503</v>
       </c>
     </row>
     <row r="113">
@@ -1829,7 +1829,7 @@
         <v>2025</v>
       </c>
       <c r="D113">
-        <v>309.5418694761537</v>
+        <v>309.5418694762384</v>
       </c>
     </row>
     <row r="114">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>312.1447524334426</v>
+        <v>353.8402797881486</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>355.778231986671</v>
+        <v>403.9525466959049</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>406.3494907363517</v>
+        <v>461.2556457252903</v>
       </c>
     </row>
     <row r="117">
@@ -1881,7 +1881,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>121.3333677022547</v>
+        <v>121.333367705715</v>
       </c>
     </row>
     <row r="118">
@@ -1894,7 +1894,7 @@
         <v>2025</v>
       </c>
       <c r="D118">
-        <v>124.5855086503369</v>
+        <v>124.5855086506281</v>
       </c>
     </row>
     <row r="119">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>128.3142626059436</v>
+        <v>139.0239114677914</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>137.7429857031163</v>
+        <v>149.6195369949708</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>150.740958249835</v>
+        <v>163.5794262925567</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>0.07042459111537287</v>
+        <v>0.07037510557082054</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>0.07037511715613091</v>
+        <v>0.07032566637565424</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>0.07032567795282584</v>
+        <v>0.07027626191200272</v>
       </c>
     </row>
     <row r="127">
@@ -2011,7 +2011,7 @@
         <v>2024</v>
       </c>
       <c r="D127">
-        <v>12.36891999106575</v>
+        <v>12.36891999106574</v>
       </c>
     </row>
     <row r="128">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>13.08054250072497</v>
+        <v>14.17228180024737</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>14.04169899839689</v>
+        <v>15.25238948408151</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>15.36670887014522</v>
+        <v>16.67545532610676</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>9.718455658195774</v>
+        <v>9.718455696198662</v>
       </c>
     </row>
     <row r="133">
@@ -2089,7 +2089,7 @@
         <v>2025</v>
       </c>
       <c r="D133">
-        <v>9.978934219341129</v>
+        <v>9.978934216481441</v>
       </c>
     </row>
     <row r="134">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>10.27760050944226</v>
+        <v>11.13541167118522</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>11.03281043060604</v>
+        <v>11.98408542155494</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>12.07390956580816</v>
+        <v>13.10223163015638</v>
       </c>
     </row>
     <row r="137">
@@ -2141,7 +2141,7 @@
         <v>2024</v>
       </c>
       <c r="D137">
-        <v>4.711979383909905</v>
+        <v>4.711979383910559</v>
       </c>
     </row>
     <row r="138">
@@ -2154,7 +2154,7 @@
         <v>2025</v>
       </c>
       <c r="D138">
-        <v>4.838270836817566</v>
+        <v>4.83827083681799</v>
       </c>
     </row>
     <row r="139">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>4.983079289139964</v>
+        <v>5.398987646693371</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>5.349241209072122</v>
+        <v>5.810465143707416</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>5.85401646335573</v>
+        <v>6.352596599669846</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>478.6869009259868</v>
+        <v>518.6401427977809</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>513.8616121878063</v>
+        <v>558.1681199968049</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>562.3516360400494</v>
+        <v>610.2466453255623</v>
       </c>
     </row>
     <row r="147">
@@ -2271,7 +2271,7 @@
         <v>2024</v>
       </c>
       <c r="D147">
-        <v>474.1423620116424</v>
+        <v>474.1414871060121</v>
       </c>
     </row>
     <row r="148">
@@ -2284,7 +2284,7 @@
         <v>2025</v>
       </c>
       <c r="D148">
-        <v>486.85119495332</v>
+        <v>486.8498078402669</v>
       </c>
     </row>
     <row r="149">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>501.4221916978104</v>
+        <v>543.270716900537</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>538.2675328167235</v>
+        <v>584.675199614866</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>589.0605967953221</v>
+        <v>639.2260782202354</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>253.268631544815</v>
+        <v>253.2686315448149</v>
       </c>
     </row>
     <row r="153">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>267.8404369966616</v>
+        <v>290.1955333327189</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>287.5217777851993</v>
+        <v>312.3126539104283</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>314.6534726137159</v>
+        <v>341.4522305980007</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>459.9267422539064</v>
+        <v>459.9267438057939</v>
       </c>
     </row>
     <row r="158">
@@ -2414,7 +2414,7 @@
         <v>2025</v>
       </c>
       <c r="D158">
-        <v>472.2716327447824</v>
+        <v>472.2716326175338</v>
       </c>
     </row>
     <row r="159">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>486.402046924702</v>
+        <v>527.0077665947492</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>522.1556789787112</v>
+        <v>567.1876383872835</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>571.4375126263741</v>
+        <v>620.1171338696505</v>
       </c>
     </row>
     <row r="162">
@@ -2466,7 +2466,7 @@
         <v>2024</v>
       </c>
       <c r="D162">
-        <v>151.5632494713665</v>
+        <v>151.563249471368</v>
       </c>
     </row>
     <row r="163">
@@ -2479,7 +2479,7 @@
         <v>2025</v>
       </c>
       <c r="D163">
-        <v>169.3712147241695</v>
+        <v>169.3712147241728</v>
       </c>
     </row>
     <row r="164">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>171.1615999981518</v>
+        <v>192.5503357989247</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>193.334454380787</v>
+        <v>218.0818126192806</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>219.2777882589955</v>
+        <v>247.2012163588069</v>
       </c>
     </row>
     <row r="167">
@@ -2531,7 +2531,7 @@
         <v>2024</v>
       </c>
       <c r="D167">
-        <v>566.7078604506023</v>
+        <v>566.7078604506024</v>
       </c>
     </row>
     <row r="168">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>647.8430115230807</v>
+        <v>734.3803152141933</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>738.4024592628648</v>
+        <v>838.3862036699547</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>843.3609593244752</v>
+        <v>957.3163590892779</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>432.8874219373189</v>
+        <v>432.8874219372402</v>
       </c>
     </row>
     <row r="173">
@@ -2609,7 +2609,7 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>490.7370712142963</v>
+        <v>490.7370712142223</v>
       </c>
     </row>
     <row r="174">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>494.8635832157671</v>
+        <v>560.9662564955833</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>564.0386231581898</v>
+        <v>640.4125417644593</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>644.2125752899324</v>
+        <v>731.2589276093629</v>
       </c>
     </row>
     <row r="177">
@@ -2661,7 +2661,7 @@
         <v>2024</v>
       </c>
       <c r="D177">
-        <v>411.1087963198651</v>
+        <v>411.1087963198014</v>
       </c>
     </row>
     <row r="178">
@@ -2674,7 +2674,7 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>466.0778992339257</v>
+        <v>466.0778992338852</v>
       </c>
     </row>
     <row r="179">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>470.0031888753328</v>
+        <v>532.822871072162</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>535.7442143748698</v>
+        <v>608.3318728184345</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>611.946044958666</v>
+        <v>694.6833909852754</v>
       </c>
     </row>
     <row r="182">
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D182">
-        <v>441.2154585406785</v>
+        <v>441.2154585407</v>
       </c>
     </row>
     <row r="183">
@@ -2739,7 +2739,7 @@
         <v>2025</v>
       </c>
       <c r="D183">
-        <v>475.4873748239368</v>
+        <v>475.4873748240065</v>
       </c>
     </row>
     <row r="184">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>483.4161797251666</v>
+        <v>533.5457058109899</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>532.7142858181401</v>
+        <v>589.1097768197625</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>592.4406859360114</v>
+        <v>654.6665751777749</v>
       </c>
     </row>
     <row r="187">
@@ -2791,7 +2791,7 @@
         <v>2024</v>
       </c>
       <c r="D187">
-        <v>809.7651300313039</v>
+        <v>809.7651300313038</v>
       </c>
     </row>
     <row r="188">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>886.0019079007556</v>
+        <v>976.9209238651692</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>975.1270432254784</v>
+        <v>1077.140536005473</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>1083.273047169405</v>
+        <v>1195.757681637572</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>772.1329525027923</v>
+        <v>845.5986058303505</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>845.255110576701</v>
+        <v>927.1224794845733</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>931.1521461334765</v>
+        <v>1020.735353085506</v>
       </c>
     </row>
     <row r="197">
@@ -2921,7 +2921,7 @@
         <v>2024</v>
       </c>
       <c r="D197">
-        <v>817.7831215532382</v>
+        <v>817.7831215531043</v>
       </c>
     </row>
     <row r="198">
@@ -2934,7 +2934,7 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>849.5272858256141</v>
+        <v>849.5272858255213</v>
       </c>
     </row>
     <row r="199">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>869.0941414939866</v>
+        <v>939.9720171029107</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>934.0309356339786</v>
+        <v>1012.593503972993</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>1018.611419731712</v>
+        <v>1103.268738118509</v>
       </c>
     </row>
     <row r="202">
@@ -2986,7 +2986,7 @@
         <v>2024</v>
       </c>
       <c r="D202">
-        <v>456.7661484464652</v>
+        <v>456.7661484464653</v>
       </c>
     </row>
     <row r="203">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>483.0456763880356</v>
+        <v>523.3621113244737</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>518.5400636790301</v>
+        <v>563.2493103194486</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>567.4708586381279</v>
+        <v>615.8011542704612</v>
       </c>
     </row>
     <row r="207">
@@ -3051,7 +3051,7 @@
         <v>2024</v>
       </c>
       <c r="D207">
-        <v>882.9059440895545</v>
+        <v>882.9059440895542</v>
       </c>
     </row>
     <row r="208">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>933.7041388735365</v>
+        <v>1011.635068591567</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>1002.314358927819</v>
+        <v>1088.736604252402</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>1096.896736188696</v>
+        <v>1190.318535722118</v>
       </c>
     </row>
     <row r="212">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>856.4747153140023</v>
+        <v>856.4747153140024</v>
       </c>
     </row>
     <row r="213">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>905.9051538948916</v>
+        <v>968.042158967089</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>965.2937295220116</v>
+        <v>1034.640442195362</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>1038.031884604128</v>
+        <v>1111.413052649932</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>1073.414016853346</v>
+        <v>1073.414016853076</v>
       </c>
     </row>
     <row r="218">
@@ -3194,7 +3194,7 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>1111.694422485196</v>
+        <v>1111.694422485105</v>
       </c>
     </row>
     <row r="219">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>1134.726249405795</v>
+        <v>1219.070308878593</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>1212.542357614179</v>
+        <v>1306.862341478286</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>1313.184571491986</v>
+        <v>1413.621064118328</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>695.7557564746498</v>
+        <v>750.0936831067098</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>747.8615368162715</v>
+        <v>807.7779330977596</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>811.1072888442009</v>
+        <v>875.4502503281331</v>
       </c>
     </row>
     <row r="227">
@@ -3311,7 +3311,7 @@
         <v>2024</v>
       </c>
       <c r="D227">
-        <v>891.1896794725806</v>
+        <v>891.1896794735003</v>
       </c>
     </row>
     <row r="228">
@@ -3324,7 +3324,7 @@
         <v>2025</v>
       </c>
       <c r="D228">
-        <v>958.9124954823056</v>
+        <v>958.9124954839544</v>
       </c>
     </row>
     <row r="229">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>960.6523296619008</v>
+        <v>1031.854814033419</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>1033.695454052958</v>
+        <v>1110.319052649402</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>1112.311143706708</v>
+        <v>1194.759564448409</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024</v>
       </c>
       <c r="D232">
-        <v>1062.765139765097</v>
+        <v>1062.765139765096</v>
       </c>
     </row>
     <row r="233">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>1145.71613955559</v>
+        <v>1230.706172968368</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>1232.918914314355</v>
+        <v>1324.373464041391</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>1326.747854336849</v>
+        <v>1425.163926000787</v>
       </c>
     </row>
     <row r="237">
@@ -3441,7 +3441,7 @@
         <v>2024</v>
       </c>
       <c r="D237">
-        <v>544.981926854869</v>
+        <v>544.9819268548689</v>
       </c>
     </row>
     <row r="238">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>577.3611503047482</v>
+        <v>612.2494255800269</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>612.5878474307602</v>
+        <v>650.6620182329051</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>651.5783238669852</v>
+        <v>691.8235277880237</v>
       </c>
     </row>
     <row r="242">
@@ -3506,7 +3506,7 @@
         <v>2024</v>
       </c>
       <c r="D242">
-        <v>401.9727924929685</v>
+        <v>401.9727924929686</v>
       </c>
     </row>
     <row r="243">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>425.8555769691918</v>
+        <v>451.5890342881355</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>451.8386566455881</v>
+        <v>479.9220315221573</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>480.5979014502663</v>
+        <v>510.2826385405062</v>
       </c>
     </row>
     <row r="247">
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
       <c r="D247">
-        <v>527.8036202937785</v>
+        <v>527.8036202937784</v>
       </c>
     </row>
     <row r="248">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>559.1622185523483</v>
+        <v>592.9507824350743</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>593.2785363589531</v>
+        <v>630.1525737135929</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>631.0399966482996</v>
+        <v>670.0166337962318</v>
       </c>
     </row>
     <row r="252">
@@ -3636,7 +3636,7 @@
         <v>2024</v>
       </c>
       <c r="D252">
-        <v>748.5448614654855</v>
+        <v>748.5448614654854</v>
       </c>
     </row>
     <row r="253">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>793.0184935802469</v>
+        <v>840.9383493241454</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>841.4031860259211</v>
+        <v>893.6989388025078</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>894.9575044789609</v>
+        <v>950.2352253102298</v>
       </c>
     </row>
     <row r="257">
@@ -3701,7 +3701,7 @@
         <v>2024</v>
       </c>
       <c r="D257">
-        <v>484.85785266098</v>
+        <v>484.8578526609714</v>
       </c>
     </row>
     <row r="258">
@@ -3714,7 +3714,7 @@
         <v>2025</v>
       </c>
       <c r="D258">
-        <v>511.4326390143365</v>
+        <v>511.4326390143664</v>
       </c>
     </row>
     <row r="259">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>513.6648887987041</v>
+        <v>544.7041747208472</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>545.0052589709585</v>
+        <v>578.8789631778259</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>579.6941793469065</v>
+        <v>615.4994001422966</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>793.6474409097</v>
+        <v>839.6465954925263</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>839.6442466852392</v>
+        <v>890.0178428718175</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>891.3286378598468</v>
+        <v>944.321475215197</v>
       </c>
     </row>
     <row r="267">
@@ -3831,7 +3831,7 @@
         <v>2024</v>
       </c>
       <c r="D267">
-        <v>353.9595251129998</v>
+        <v>353.9595251128844</v>
       </c>
     </row>
     <row r="268">
@@ -3844,7 +3844,7 @@
         <v>2025</v>
       </c>
       <c r="D268">
-        <v>373.3489045821721</v>
+        <v>373.348904582185</v>
       </c>
     </row>
     <row r="269">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>375.0005791175017</v>
+        <v>397.6933076573733</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>397.907874921703</v>
+        <v>422.6814125257156</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>423.2804984432607</v>
+        <v>449.4667751470248</v>
       </c>
     </row>
     <row r="272">
@@ -3896,7 +3896,7 @@
         <v>2024</v>
       </c>
       <c r="D272">
-        <v>330.376002896221</v>
+        <v>330.3760028962209</v>
       </c>
     </row>
     <row r="273">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>346.9822032279101</v>
+        <v>373.3824755944287</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>368.9912561508597</v>
+        <v>396.4031616650694</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>399.9634190817317</v>
+        <v>430.1046199856971</v>
       </c>
     </row>
     <row r="277">
@@ -3961,7 +3961,7 @@
         <v>2024</v>
       </c>
       <c r="D277">
-        <v>8.177966912195908</v>
+        <v>8.177966912196041</v>
       </c>
     </row>
     <row r="278">
@@ -3974,7 +3974,7 @@
         <v>2025</v>
       </c>
       <c r="D278">
-        <v>9.003823029294889</v>
+        <v>9.003823029295065</v>
       </c>
     </row>
     <row r="279">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>9.069859476758898</v>
+        <v>10.02778848878615</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>10.05878854812133</v>
+        <v>11.14475412628358</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>11.1878118466773</v>
+        <v>12.39089292496327</v>
       </c>
     </row>
     <row r="282">
@@ -4026,7 +4026,7 @@
         <v>2024</v>
       </c>
       <c r="D282">
-        <v>122.0560884262384</v>
+        <v>122.0560884262402</v>
       </c>
     </row>
     <row r="283">
@@ -4039,7 +4039,7 @@
         <v>2025</v>
       </c>
       <c r="D283">
-        <v>134.382034328057</v>
+        <v>134.3820343280545</v>
       </c>
     </row>
     <row r="284">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>135.3676155634875</v>
+        <v>149.6647239361621</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>150.127405104186</v>
+        <v>166.3354570483248</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>166.9780938839094</v>
+        <v>184.9341006672136</v>
       </c>
     </row>
     <row r="287">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>503.3534388903619</v>
+        <v>503.3534388903618</v>
       </c>
     </row>
     <row r="288">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>558.2496182355269</v>
+        <v>617.2102610460253</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>619.1183478203986</v>
+        <v>685.9596276449771</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>688.609832592963</v>
+        <v>762.659609087887</v>
       </c>
     </row>
     <row r="292">
@@ -4156,7 +4156,7 @@
         <v>2024</v>
       </c>
       <c r="D292">
-        <v>502.3311924191593</v>
+        <v>502.3311924190456</v>
       </c>
     </row>
     <row r="293">
@@ -4169,7 +4169,7 @@
         <v>2025</v>
       </c>
       <c r="D293">
-        <v>553.059676481968</v>
+        <v>553.0596764818457</v>
       </c>
     </row>
     <row r="294">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>557.1158852885777</v>
+        <v>615.9567869644241</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>617.8609987603373</v>
+        <v>684.5665328342011</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>687.2113555582881</v>
+        <v>761.1107468755139</v>
       </c>
     </row>
     <row r="297">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>344.8812790495485</v>
+        <v>381.3065910725508</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>382.4853864688702</v>
+        <v>423.7792814332606</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>425.4165524809964</v>
+        <v>471.1637849371779</v>
       </c>
     </row>
     <row r="302">
@@ -4286,7 +4286,7 @@
         <v>2024</v>
       </c>
       <c r="D302">
-        <v>434.2496893405167</v>
+        <v>434.2496893405746</v>
       </c>
     </row>
     <row r="303">
@@ -4299,7 +4299,7 @@
         <v>2025</v>
       </c>
       <c r="D303">
-        <v>478.1028756052693</v>
+        <v>478.1028756053211</v>
       </c>
     </row>
     <row r="304">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>481.6093444238084</v>
+        <v>532.4754683257121</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>534.12159906566</v>
+        <v>591.7864532661614</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>594.0728200966731</v>
+        <v>657.9565386984192</v>
       </c>
     </row>
     <row r="307">
@@ -4351,7 +4351,7 @@
         <v>2024</v>
       </c>
       <c r="D307">
-        <v>21.09694227612195</v>
+        <v>21.09694227609011</v>
       </c>
     </row>
     <row r="308">
@@ -4364,7 +4364,7 @@
         <v>2025</v>
       </c>
       <c r="D308">
-        <v>22.96884401595798</v>
+        <v>22.96884401597812</v>
       </c>
     </row>
     <row r="309">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>23.28718095811576</v>
+        <v>25.79575658229075</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>25.81546434363461</v>
+        <v>28.68179243273734</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>28.82383104477797</v>
+        <v>31.99394411947515</v>
       </c>
     </row>
     <row r="312">
@@ -4416,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="D312">
-        <v>413.0554869247568</v>
+        <v>413.0557528618447</v>
       </c>
     </row>
     <row r="313">
@@ -4429,7 +4429,7 @@
         <v>2025</v>
       </c>
       <c r="D313">
-        <v>449.7060238841045</v>
+        <v>449.7064801581701</v>
       </c>
     </row>
     <row r="314">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>455.9385102997325</v>
+        <v>505.0547749162102</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>505.4400177228665</v>
+        <v>561.5610943929213</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>564.3409425109112</v>
+        <v>626.4102929498233</v>
       </c>
     </row>
     <row r="317">
@@ -4481,7 +4481,7 @@
         <v>2024</v>
       </c>
       <c r="D317">
-        <v>470.4245823984662</v>
+        <v>470.4245823972534</v>
       </c>
     </row>
     <row r="318">
@@ -4494,7 +4494,7 @@
         <v>2025</v>
       </c>
       <c r="D318">
-        <v>512.1657196764019</v>
+        <v>512.1657196787928</v>
       </c>
     </row>
     <row r="319">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>519.2638590628191</v>
+        <v>575.2012751169517</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>575.6409024915578</v>
+        <v>639.5557126910247</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>642.7229147974448</v>
+        <v>713.4117566031598</v>
       </c>
     </row>
     <row r="322">
@@ -4546,7 +4546,7 @@
         <v>2024</v>
       </c>
       <c r="D322">
-        <v>217.8165037571726</v>
+        <v>217.816642721158</v>
       </c>
     </row>
     <row r="323">
@@ -4559,7 +4559,7 @@
         <v>2025</v>
       </c>
       <c r="D323">
-        <v>237.1433509671593</v>
+        <v>237.1435918367279</v>
       </c>
     </row>
     <row r="324">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>240.4299521794401</v>
+        <v>266.3303999662334</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>266.5335341033103</v>
+        <v>296.127822769319</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>297.593722953286</v>
+        <v>330.3247072695507</v>
       </c>
     </row>
     <row r="327">
@@ -4611,7 +4611,7 @@
         <v>2024</v>
       </c>
       <c r="D327">
-        <v>603.076292122001</v>
+        <v>603.0762921220914</v>
       </c>
     </row>
     <row r="328">
@@ -4624,7 +4624,7 @@
         <v>2025</v>
       </c>
       <c r="D328">
-        <v>635.2035798518136</v>
+        <v>635.2035798518639</v>
       </c>
     </row>
     <row r="329">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>647.7315205782382</v>
+        <v>704.9146897610043</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>702.6272323142916</v>
+        <v>767.7634273302713</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>771.509044819088</v>
+        <v>841.8490173663497</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>815.468989137651</v>
+        <v>878.528356348825</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>868.406376546774</v>
+        <v>934.2162279627098</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>942.5258873236793</v>
+        <v>1014.833077659503</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>653.0077906512739</v>
+        <v>703.5042020039771</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>695.3987359464817</v>
+        <v>748.0976447950012</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>754.7518388444888</v>
+        <v>812.6536697344886</v>
       </c>
     </row>
     <row r="342">
@@ -4806,7 +4806,7 @@
         <v>2024</v>
       </c>
       <c r="D342">
-        <v>273.6882001635229</v>
+        <v>273.6882001635228</v>
       </c>
     </row>
     <row r="343">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>287.8295148161653</v>
+        <v>310.087070436996</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>306.5143332201775</v>
+        <v>329.7426553755597</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>332.6756919073493</v>
+        <v>358.1973499094925</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>209.1550254979</v>
+        <v>209.1550027871474</v>
       </c>
     </row>
     <row r="348">
@@ -4884,7 +4884,7 @@
         <v>2025</v>
       </c>
       <c r="D348">
-        <v>223.2752162936632</v>
+        <v>223.2752122751706</v>
       </c>
     </row>
     <row r="349">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>227.2273482758712</v>
+        <v>249.2517869468478</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>248.6773099099211</v>
+        <v>273.5049008062965</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>274.9556038240949</v>
+        <v>302.1100848045705</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>344.0280907266185</v>
+        <v>344.0280907257577</v>
       </c>
     </row>
     <row r="353">
@@ -4949,7 +4949,7 @@
         <v>2025</v>
       </c>
       <c r="D353">
-        <v>374.5539128505552</v>
+        <v>374.5539128518223</v>
       </c>
     </row>
     <row r="354">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>379.7449000668192</v>
+        <v>420.6526966250163</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>420.9741905790403</v>
+        <v>467.7159622666983</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>470.0321846394615</v>
+        <v>521.7278950367463</v>
       </c>
     </row>
     <row r="357">
@@ -5001,7 +5001,7 @@
         <v>2024</v>
       </c>
       <c r="D357">
-        <v>295.2893790683704</v>
+        <v>295.2893790692449</v>
       </c>
     </row>
     <row r="358">
@@ -5014,7 +5014,7 @@
         <v>2025</v>
       </c>
       <c r="D358">
-        <v>321.1130917324767</v>
+        <v>321.1130917318832</v>
       </c>
     </row>
     <row r="359">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>325.6276792647691</v>
+        <v>360.4805669927744</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>360.6966458467539</v>
+        <v>400.4962788126294</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>402.4800467229963</v>
+        <v>446.4632943587117</v>
       </c>
     </row>
     <row r="362">
@@ -5066,7 +5066,7 @@
         <v>2024</v>
       </c>
       <c r="D362">
-        <v>690.3721208015639</v>
+        <v>690.3721208015637</v>
       </c>
     </row>
     <row r="363">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>726.0434431081871</v>
+        <v>782.1876250002584</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>773.1756194550671</v>
+        <v>831.7686498422039</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>839.1670710934072</v>
+        <v>903.5449384377599</v>
       </c>
     </row>
     <row r="367">
@@ -5131,7 +5131,7 @@
         <v>2024</v>
       </c>
       <c r="D367">
-        <v>510.4652975507703</v>
+        <v>510.4652988901715</v>
       </c>
     </row>
     <row r="368">
@@ -5144,7 +5144,7 @@
         <v>2025</v>
       </c>
       <c r="D368">
-        <v>521.7030488799254</v>
+        <v>521.7030491240508</v>
       </c>
     </row>
     <row r="369">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>536.8408443314225</v>
+        <v>578.3541880201069</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>571.6906222486999</v>
+        <v>615.0146322341448</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>620.4850909084321</v>
+        <v>668.0864565531751</v>
       </c>
     </row>
     <row r="372">
@@ -5196,7 +5196,7 @@
         <v>2024</v>
       </c>
       <c r="D372">
-        <v>687.911388278451</v>
+        <v>687.9113882784511</v>
       </c>
     </row>
     <row r="373">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>723.4555660398811</v>
+        <v>779.3996303832861</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>770.4197472315687</v>
+        <v>828.8039318535137</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>836.175982255435</v>
+        <v>900.3243845295049</v>
       </c>
     </row>
     <row r="377">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>518.6676217237273</v>
+        <v>518.6676198555119</v>
       </c>
     </row>
     <row r="378">
@@ -5274,7 +5274,7 @@
         <v>2025</v>
       </c>
       <c r="D378">
-        <v>529.3941602880252</v>
+        <v>529.3941592964453</v>
       </c>
     </row>
     <row r="379">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>544.7704230667631</v>
+        <v>586.249484439281</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>579.3610375320014</v>
+        <v>622.4394624846428</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>628.0273851706725</v>
+        <v>675.3931991889356</v>
       </c>
     </row>
     <row r="382">
@@ -5326,7 +5326,7 @@
         <v>2024</v>
       </c>
       <c r="D382">
-        <v>366.1819472218901</v>
+        <v>366.1819481539349</v>
       </c>
     </row>
     <row r="383">
@@ -5339,7 +5339,7 @@
         <v>2025</v>
       </c>
       <c r="D383">
-        <v>409.3748658746666</v>
+        <v>409.3748658949492</v>
       </c>
     </row>
     <row r="384">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>417.6560689393006</v>
+        <v>477.411394210347</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>478.2185403473132</v>
+        <v>547.869361493463</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>552.6235761279457</v>
+        <v>632.5899732813481</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>647.0587171449029</v>
+        <v>724.8466264410283</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>727.611944803316</v>
+        <v>816.6938856453994</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>820.8026168933798</v>
+        <v>920.8673385937117</v>
       </c>
     </row>
     <row r="392">
@@ -5456,7 +5456,7 @@
         <v>2024</v>
       </c>
       <c r="D392">
-        <v>169.5029136914006</v>
+        <v>169.5029136914014</v>
       </c>
     </row>
     <row r="393">
@@ -5469,7 +5469,7 @@
         <v>2025</v>
       </c>
       <c r="D393">
-        <v>173.8534950732159</v>
+        <v>173.8534950732412</v>
       </c>
     </row>
     <row r="394">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>175.4545892565546</v>
+        <v>183.0073590050835</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>182.6284407934226</v>
+        <v>191.0244683020606</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>191.3240146089757</v>
+        <v>199.9402165199493</v>
       </c>
     </row>
     <row r="397">
@@ -5521,7 +5521,7 @@
         <v>2024</v>
       </c>
       <c r="D397">
-        <v>256.3869120370131</v>
+        <v>256.3869120371943</v>
       </c>
     </row>
     <row r="398">
@@ -5534,7 +5534,7 @@
         <v>2025</v>
       </c>
       <c r="D398">
-        <v>287.0334398476563</v>
+        <v>287.0334398477703</v>
       </c>
     </row>
     <row r="399">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>289.7167279158392</v>
+        <v>325.7298318630201</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>327.0736048477741</v>
+        <v>368.4575428330052</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>370.4315967554758</v>
+        <v>417.1074155709845</v>
       </c>
     </row>
     <row r="402">
@@ -5586,7 +5586,7 @@
         <v>2024</v>
       </c>
       <c r="D402">
-        <v>692.1432517025096</v>
+        <v>692.1432517025095</v>
       </c>
     </row>
     <row r="403">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>780.8182588070564</v>
+        <v>876.4991786983242</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>880.0336269662356</v>
+        <v>989.7893561800469</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>994.9356608878816</v>
+        <v>1118.518447785274</v>
       </c>
     </row>
     <row r="407">
@@ -5651,7 +5651,7 @@
         <v>2024</v>
       </c>
       <c r="D407">
-        <v>428.9381819946743</v>
+        <v>428.9381808607847</v>
       </c>
     </row>
     <row r="408">
@@ -5664,7 +5664,7 @@
         <v>2025</v>
       </c>
       <c r="D408">
-        <v>486.493193178921</v>
+        <v>486.4931930074057</v>
       </c>
     </row>
     <row r="409">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>494.455345104469</v>
+        <v>567.9346595747413</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>570.4110529627559</v>
+        <v>656.8053054052006</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>662.2172022735244</v>
+        <v>761.9116410366969</v>
       </c>
     </row>
     <row r="412">
@@ -5716,7 +5716,7 @@
         <v>2024</v>
       </c>
       <c r="D412">
-        <v>499.7266457155856</v>
+        <v>499.7266457155855</v>
       </c>
     </row>
     <row r="413">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>576.4777782600435</v>
+        <v>662.7366428593934</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>665.5991079652134</v>
+        <v>767.0906348310957</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>773.5309208427537</v>
+        <v>890.765484837772</v>
       </c>
     </row>
     <row r="417">
@@ -5781,7 +5781,7 @@
         <v>2024</v>
       </c>
       <c r="D417">
-        <v>784.340300083393</v>
+        <v>784.3403000833929</v>
       </c>
     </row>
     <row r="418">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>883.2560730127116</v>
+        <v>989.8545014421899</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>993.7423859794006</v>
+        <v>1115.79923898346</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>1121.421831012497</v>
+        <v>1258.611752611841</v>
       </c>
     </row>
     <row r="422">
@@ -5846,7 +5846,7 @@
         <v>2024</v>
       </c>
       <c r="D422">
-        <v>140.1318181914859</v>
+        <v>140.1320106192227</v>
       </c>
     </row>
     <row r="423">
@@ -5859,7 +5859,7 @@
         <v>2025</v>
       </c>
       <c r="D423">
-        <v>143.7285141453103</v>
+        <v>143.7287915531081</v>
       </c>
     </row>
     <row r="424">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>145.0521739872713</v>
+        <v>151.2966242179123</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>150.9829283245658</v>
+        <v>157.9246577083966</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>158.1717220926136</v>
+        <v>165.2956383946899</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>347.4904046263325</v>
+        <v>362.448795798867</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>361.6983608408341</v>
+        <v>378.3268374702905</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>378.9200861751747</v>
+        <v>395.9846252563665</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>135.0597071870887</v>
+        <v>135.0597071871298</v>
       </c>
     </row>
     <row r="433">
@@ -5989,7 +5989,7 @@
         <v>2025</v>
       </c>
       <c r="D433">
-        <v>138.5262172414213</v>
+        <v>138.5262172414902</v>
       </c>
     </row>
     <row r="434">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>139.8019673658559</v>
+        <v>145.8199776691643</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>145.5180546233531</v>
+        <v>152.2079689597248</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>152.4466464977552</v>
+        <v>159.3119928648144</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>218.1007450019337</v>
+        <v>218.1007450019289</v>
       </c>
     </row>
     <row r="438">
@@ -6054,7 +6054,7 @@
         <v>2025</v>
       </c>
       <c r="D438">
-        <v>223.6986692337865</v>
+        <v>223.6986692337947</v>
       </c>
     </row>
     <row r="439">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>225.7587945576532</v>
+        <v>235.4769694372502</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>234.989418127822</v>
+        <v>245.7926157124595</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>246.1780401766622</v>
+        <v>257.2645353803333</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>708.4858596949252</v>
+        <v>708.4858596949251</v>
       </c>
     </row>
     <row r="443">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>730.4106870570023</v>
+        <v>766.0669170475857</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>760.3468556443163</v>
+        <v>798.294365456867</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>802.018199687847</v>
+        <v>841.6933165590883</v>
       </c>
     </row>
     <row r="447">
@@ -6171,7 +6171,7 @@
         <v>2024</v>
       </c>
       <c r="D447">
-        <v>1011.033556597514</v>
+        <v>1011.033556597332</v>
       </c>
     </row>
     <row r="448">
@@ -6184,7 +6184,7 @@
         <v>2025</v>
       </c>
       <c r="D448">
-        <v>1022.51968583906</v>
+        <v>1022.519685838687</v>
       </c>
     </row>
     <row r="449">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>1042.253377179824</v>
+        <v>1093.206889102346</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>1084.948300237834</v>
+        <v>1139.118325770762</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>1144.495946276567</v>
+        <v>1201.162623954247</v>
       </c>
     </row>
     <row r="452">
@@ -6236,7 +6236,7 @@
         <v>2024</v>
       </c>
       <c r="D452">
-        <v>1339.930120719956</v>
+        <v>1339.930120720227</v>
       </c>
     </row>
     <row r="453">
@@ -6249,7 +6249,7 @@
         <v>2025</v>
       </c>
       <c r="D453">
-        <v>1355.153120796934</v>
+        <v>1355.153120797303</v>
       </c>
     </row>
     <row r="454">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>1381.306263161098</v>
+        <v>1448.835547967014</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>1437.890440503495</v>
+        <v>1509.68265274794</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>1516.809627050591</v>
+        <v>1591.910680439263</v>
       </c>
     </row>
     <row r="457">
@@ -6301,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="D457">
-        <v>843.9005456420684</v>
+        <v>843.9005456420682</v>
       </c>
     </row>
     <row r="458">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>869.9697716365916</v>
+        <v>912.4895845924925</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>905.6107417424059</v>
+        <v>950.8234559595114</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>955.3024663582213</v>
+        <v>1002.59435852266</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>108.9914537589748</v>
+        <v>108.9915742567495</v>
       </c>
     </row>
     <row r="463">
@@ -6379,7 +6379,7 @@
         <v>2025</v>
       </c>
       <c r="D463">
-        <v>111.7888859895648</v>
+        <v>111.7890600208759</v>
       </c>
     </row>
     <row r="464">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>112.8184071344864</v>
+        <v>117.6751542497145</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>117.4312310042406</v>
+        <v>122.8302870818815</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>123.0225370561309</v>
+        <v>128.5632703109017</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>391.2284871798105</v>
+        <v>438.4450576418235</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>440.1671439016072</v>
+        <v>494.2308523504428</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>496.7213177099629</v>
+        <v>557.4880431376225</v>
       </c>
     </row>
     <row r="472">
@@ -6496,7 +6496,7 @@
         <v>2024</v>
       </c>
       <c r="D472">
-        <v>113.5917154642921</v>
+        <v>113.5917154642362</v>
       </c>
     </row>
     <row r="473">
@@ -6509,7 +6509,7 @@
         <v>2025</v>
       </c>
       <c r="D473">
-        <v>116.5072118072096</v>
+        <v>116.5072118071598</v>
       </c>
     </row>
     <row r="474">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>117.5801829037326</v>
+        <v>122.6416214396136</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>122.3876878650357</v>
+        <v>128.0142303481023</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>128.2149705356032</v>
+        <v>133.9890598187866</v>
       </c>
     </row>
     <row r="477">
@@ -6561,7 +6561,7 @@
         <v>2024</v>
       </c>
       <c r="D477">
-        <v>301.9675455183832</v>
+        <v>301.9675455183728</v>
       </c>
     </row>
     <row r="478">
@@ -6574,7 +6574,7 @@
         <v>2025</v>
       </c>
       <c r="D478">
-        <v>309.7181269689623</v>
+        <v>309.7181269689141</v>
       </c>
     </row>
     <row r="479">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>312.5704318689848</v>
+        <v>326.0256231195384</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>325.3505982911223</v>
+        <v>340.3080447846917</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>340.8416777870486</v>
+        <v>356.1913654566044</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>140.8133752654798</v>
+        <v>140.8133752654056</v>
       </c>
     </row>
     <row r="483">
@@ -6639,7 +6639,7 @@
         <v>2025</v>
       </c>
       <c r="D483">
-        <v>144.2923337795129</v>
+        <v>144.2923337794204</v>
       </c>
     </row>
     <row r="484">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>145.7506627293201</v>
+        <v>152.1462791428193</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>151.7711192701706</v>
+        <v>158.8747448878402</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>159.1572232579295</v>
+        <v>166.4506457425432</v>
       </c>
     </row>
     <row r="487">
@@ -6691,7 +6691,7 @@
         <v>2024</v>
       </c>
       <c r="D487">
-        <v>509.2430750264721</v>
+        <v>509.2430750264554</v>
       </c>
     </row>
     <row r="488">
@@ -6704,7 +6704,7 @@
         <v>2025</v>
       </c>
       <c r="D488">
-        <v>515.0282957166535</v>
+        <v>515.0282957165889</v>
       </c>
     </row>
     <row r="489">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>524.9679559112462</v>
+        <v>550.6324969905276</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>546.4727044002884</v>
+        <v>573.7573204934662</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>576.4659871829047</v>
+        <v>605.0081440643341</v>
       </c>
     </row>
     <row r="492">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>615.6211613527761</v>
+        <v>645.7176331849345</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>640.8395291407473</v>
+        <v>672.8358540635902</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>676.0122580587504</v>
+        <v>709.4832869277262</v>
       </c>
     </row>
     <row r="497">
@@ -6821,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="D497">
-        <v>566.8745841339522</v>
+        <v>566.8745841339396</v>
       </c>
     </row>
     <row r="498">
@@ -6834,7 +6834,7 @@
         <v>2025</v>
       </c>
       <c r="D498">
-        <v>573.3146209743443</v>
+        <v>573.3146209743092</v>
       </c>
     </row>
     <row r="499">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>584.3791591079829</v>
+        <v>612.9482722156034</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>608.3177205245066</v>
+        <v>638.6902683834517</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>641.705477092352</v>
+        <v>673.4778906777881</v>
       </c>
     </row>
     <row r="502">
@@ -6886,7 +6886,7 @@
         <v>2024</v>
       </c>
       <c r="D502">
-        <v>739.7687738441812</v>
+        <v>739.7687738441811</v>
       </c>
     </row>
     <row r="503">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>762.6122193934698</v>
+        <v>799.8947891815405</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>793.851974734072</v>
+        <v>833.4880398659877</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>837.4228525739182</v>
+        <v>878.8857286742268</v>
       </c>
     </row>
     <row r="507">
@@ -6951,7 +6951,7 @@
         <v>2024</v>
       </c>
       <c r="D507">
-        <v>312.3669755810162</v>
+        <v>312.3669755810983</v>
       </c>
     </row>
     <row r="508">
@@ -6964,7 +6964,7 @@
         <v>2025</v>
       </c>
       <c r="D508">
-        <v>315.7697679671843</v>
+        <v>315.7697679672558</v>
       </c>
     </row>
     <row r="509">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>322.3844257406236</v>
+        <v>339.0165336738118</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>336.1163301820133</v>
+        <v>353.5626889053473</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>355.5026698322644</v>
+        <v>373.9287869181584</v>
       </c>
     </row>
     <row r="512">
@@ -7016,7 +7016,7 @@
         <v>2024</v>
       </c>
       <c r="D512">
-        <v>473.507390617747</v>
+        <v>473.5073906177813</v>
       </c>
     </row>
     <row r="513">
@@ -7029,7 +7029,7 @@
         <v>2025</v>
       </c>
       <c r="D513">
-        <v>507.7436081380138</v>
+        <v>507.7436081380471</v>
       </c>
     </row>
     <row r="514">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>516.1220214940085</v>
+        <v>567.1150657263285</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>565.9957071874568</v>
+        <v>623.1284476981725</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>626.4820163759636</v>
+        <v>689.2025357036442</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>334.736183775428</v>
+        <v>349.8266495620471</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>348.6291175559155</v>
+        <v>365.3217083800573</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>366.1541842028944</v>
+        <v>383.314194666579</v>
       </c>
     </row>
     <row r="522">
@@ -7146,7 +7146,7 @@
         <v>2024</v>
       </c>
       <c r="D522">
-        <v>123.6180064332254</v>
+        <v>123.6181433638956</v>
       </c>
     </row>
     <row r="523">
@@ -7159,7 +7159,7 @@
         <v>2025</v>
       </c>
       <c r="D523">
-        <v>126.7908577456746</v>
+        <v>126.7910551496274</v>
       </c>
     </row>
     <row r="524">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>127.9585372871265</v>
+        <v>133.4670569394639</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>133.1904005785657</v>
+        <v>139.3140065500557</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>139.5320558189015</v>
+        <v>145.8163521486845</v>
       </c>
     </row>
     <row r="527">
@@ -7211,7 +7211,7 @@
         <v>2024</v>
       </c>
       <c r="D527">
-        <v>552.2056617488317</v>
+        <v>552.2056617488316</v>
       </c>
     </row>
     <row r="528">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>569.6861577848892</v>
+        <v>620.161579280371</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>600.6977669427669</v>
+        <v>645.2404892224645</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>660.274093983148</v>
+        <v>715.4202134466086</v>
       </c>
     </row>
     <row r="532">
@@ -7276,7 +7276,7 @@
         <v>2024</v>
       </c>
       <c r="D532">
-        <v>785.6788833939927</v>
+        <v>785.6788833939925</v>
       </c>
     </row>
     <row r="533">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>819.7901241525459</v>
+        <v>877.2545851970723</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>865.0271230063371</v>
+        <v>921.3898799553664</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>931.0379332199574</v>
+        <v>994.4693345074336</v>
       </c>
     </row>
     <row r="537">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>870.2842505338696</v>
+        <v>931.2175038683945</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>918.3084838336972</v>
+        <v>978.1000135975946</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>988.2908117946919</v>
+        <v>1055.554917918087</v>
       </c>
     </row>
     <row r="542">
@@ -7406,7 +7406,7 @@
         <v>2024</v>
       </c>
       <c r="D542">
-        <v>1106.126771859347</v>
+        <v>1106.126768798078</v>
       </c>
     </row>
     <row r="543">
@@ -7419,7 +7419,7 @@
         <v>2025</v>
       </c>
       <c r="D543">
-        <v>1121.485636374742</v>
+        <v>1121.48563183836</v>
       </c>
     </row>
     <row r="544">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>1154.212502342502</v>
+        <v>1235.025091233193</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>1217.904580227769</v>
+        <v>1297.202995433982</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>1310.718498932808</v>
+        <v>1399.927378983442</v>
       </c>
     </row>
     <row r="547">
@@ -7471,7 +7471,7 @@
         <v>2024</v>
       </c>
       <c r="D547">
-        <v>278.0021236195432</v>
+        <v>278.0021241727302</v>
       </c>
     </row>
     <row r="548">
@@ -7484,7 +7484,7 @@
         <v>2025</v>
       </c>
       <c r="D548">
-        <v>282.0835374483543</v>
+        <v>282.0835380356701</v>
       </c>
     </row>
     <row r="549">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>290.2679643978097</v>
+        <v>310.7182332735711</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>306.4489878195138</v>
+        <v>326.5451952524051</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>329.9334240588823</v>
+        <v>352.5368480931186</v>
       </c>
     </row>
     <row r="552">
@@ -7536,7 +7536,7 @@
         <v>2024</v>
       </c>
       <c r="D552">
-        <v>758.4869549625965</v>
+        <v>758.4869549625964</v>
       </c>
     </row>
     <row r="553">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>791.4599800769614</v>
+        <v>846.8743238967439</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>835.1345029163504</v>
+        <v>889.5105234807636</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>898.7783177045612</v>
+        <v>959.9501057361767</v>
       </c>
     </row>
     <row r="557">
@@ -7601,7 +7601,7 @@
         <v>2024</v>
       </c>
       <c r="D557">
-        <v>812.3797979671789</v>
+        <v>812.3797979671791</v>
       </c>
     </row>
     <row r="558">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>866.3735417344573</v>
+        <v>936.1510933643493</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>930.3368984477444</v>
+        <v>1004.26986810704</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>1010.67396661593</v>
+        <v>1091.600938376402</v>
       </c>
     </row>
     <row r="562">
@@ -7666,7 +7666,7 @@
         <v>2024</v>
       </c>
       <c r="D562">
-        <v>494.8947878294072</v>
+        <v>494.8947873857595</v>
       </c>
     </row>
     <row r="563">
@@ -7679,7 +7679,7 @@
         <v>2025</v>
       </c>
       <c r="D563">
-        <v>533.455911144115</v>
+        <v>533.4559104612222</v>
       </c>
     </row>
     <row r="564">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>534.1674789903839</v>
+        <v>574.1517368995319</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>575.2954757461604</v>
+        <v>618.278776591966</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>619.3683211184713</v>
+        <v>665.6744452624522</v>
       </c>
     </row>
     <row r="567">
@@ -7731,7 +7731,7 @@
         <v>2024</v>
       </c>
       <c r="D567">
-        <v>1000.248975316835</v>
+        <v>1000.248975328512</v>
       </c>
     </row>
     <row r="568">
@@ -7744,7 +7744,7 @@
         <v>2025</v>
       </c>
       <c r="D568">
-        <v>1072.748003495836</v>
+        <v>1072.748003517562</v>
       </c>
     </row>
     <row r="569">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>1075.534241777848</v>
+        <v>1153.605746555045</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>1155.283611524991</v>
+        <v>1239.497084606357</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>1241.749400198879</v>
+        <v>1332.14536958147</v>
       </c>
     </row>
     <row r="572">
@@ -7796,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="D572">
-        <v>613.6951550317016</v>
+        <v>613.6951550317015</v>
       </c>
     </row>
     <row r="573">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>650.1568781831901</v>
+        <v>689.4439984566251</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>689.8250918159041</v>
+        <v>732.6997959298434</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>733.7316323939637</v>
+        <v>779.0511027954226</v>
       </c>
     </row>
     <row r="577">
@@ -7861,7 +7861,7 @@
         <v>2024</v>
       </c>
       <c r="D577">
-        <v>756.0536801108285</v>
+        <v>756.0536801108284</v>
       </c>
     </row>
     <row r="578">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>770.305567116104</v>
+        <v>801.1005983669935</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>790.2986643683513</v>
+        <v>816.0329718675707</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>824.0417920823365</v>
+        <v>854.9918060124453</v>
       </c>
     </row>
     <row r="582">
@@ -7926,7 +7926,7 @@
         <v>2024</v>
       </c>
       <c r="D582">
-        <v>1361.494299079141</v>
+        <v>1361.494283133745</v>
       </c>
     </row>
     <row r="583">
@@ -7939,7 +7939,7 @@
         <v>2025</v>
       </c>
       <c r="D583">
-        <v>1357.368477672455</v>
+        <v>1357.368455256875</v>
       </c>
     </row>
     <row r="584">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>1387.159107889234</v>
+        <v>1442.614510376391</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>1423.162641470589</v>
+        <v>1469.504853003292</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>1483.92700691112</v>
+        <v>1539.66151293777</v>
       </c>
     </row>
     <row r="587">
@@ -7991,7 +7991,7 @@
         <v>2024</v>
       </c>
       <c r="D587">
-        <v>506.2272420682913</v>
+        <v>506.2272420682912</v>
       </c>
     </row>
     <row r="588">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>515.7697692700179</v>
+        <v>536.3890381927843</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>529.156408805758</v>
+        <v>546.3871606755116</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>551.7496143929073</v>
+        <v>572.4726443104262</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>697.4736317419432</v>
+        <v>726.9570513017394</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>718.9972103599339</v>
+        <v>746.1868480172838</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>751.8264518519812</v>
+        <v>782.3354562369204</v>
       </c>
     </row>
     <row r="597">
@@ -8121,7 +8121,7 @@
         <v>2024</v>
       </c>
       <c r="D597">
-        <v>399.3957694830552</v>
+        <v>399.3957694830017</v>
       </c>
     </row>
     <row r="598">
@@ -8134,7 +8134,7 @@
         <v>2025</v>
       </c>
       <c r="D598">
-        <v>421.2864070275504</v>
+        <v>421.2864070275627</v>
       </c>
     </row>
     <row r="599">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>423.1252007767853</v>
+        <v>448.69342581978</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>448.9414380597102</v>
+        <v>476.8444813318981</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>477.516005957443</v>
+        <v>507.0101107208552</v>
       </c>
     </row>
     <row r="602">
@@ -8186,7 +8186,7 @@
         <v>2024</v>
       </c>
       <c r="D602">
-        <v>919.7147482690093</v>
+        <v>919.7147482690089</v>
       </c>
     </row>
     <row r="603">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>987.346024100812</v>
+        <v>1057.935222340891</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>1059.294563575179</v>
+        <v>1135.560366692109</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>1137.613149775528</v>
+        <v>1219.343860293583</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>1410.951925187327</v>
+        <v>1516.566695150809</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>1519.587766150644</v>
+        <v>1633.124253119437</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>1636.002194110945</v>
+        <v>1758.31563406259</v>
       </c>
     </row>
     <row r="612">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>624.0248357702733</v>
+        <v>624.0248357702731</v>
       </c>
     </row>
     <row r="613">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>670.6138818948428</v>
+        <v>719.0413119675471</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>720.0417843595129</v>
+        <v>772.3085431642835</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>773.7108747126819</v>
+        <v>829.7827690062151</v>
       </c>
     </row>
     <row r="617">
@@ -8381,7 +8381,7 @@
         <v>2024</v>
       </c>
       <c r="D617">
-        <v>632.2314303116118</v>
+        <v>632.231430311612</v>
       </c>
     </row>
     <row r="618">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>679.9942391420171</v>
+        <v>731.170586172086</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>731.9206648830274</v>
+        <v>788.0107075346425</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>789.6990213030227</v>
+        <v>849.9157702023399</v>
       </c>
     </row>
     <row r="622">
@@ -8446,7 +8446,7 @@
         <v>2024</v>
       </c>
       <c r="D622">
-        <v>841.3254917221218</v>
+        <v>841.3254917221216</v>
       </c>
     </row>
     <row r="623">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>890.1632430988669</v>
+        <v>945.2996417377614</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>944.8914416475382</v>
+        <v>1005.510087368136</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>1007.381386536571</v>
+        <v>1071.334430503815</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>677.7470856335439</v>
+        <v>704.8418358018954</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>695.3378290435616</v>
+        <v>717.9799284252881</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>725.026434989902</v>
+        <v>752.2575407425226</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>1070.428581944281</v>
+        <v>1070.42858195118</v>
       </c>
     </row>
     <row r="633">
@@ -8589,7 +8589,7 @@
         <v>2025</v>
       </c>
       <c r="D633">
-        <v>1067.184715776134</v>
+        <v>1067.184715785059</v>
       </c>
     </row>
     <row r="634">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>1090.606622245663</v>
+        <v>1134.206569031827</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>1118.913131385012</v>
+        <v>1155.34810938119</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>1166.687034404544</v>
+        <v>1210.506424859835</v>
       </c>
     </row>
     <row r="637">
@@ -8641,7 +8641,7 @@
         <v>2024</v>
       </c>
       <c r="D637">
-        <v>492.4808235522179</v>
+        <v>492.4808170170542</v>
       </c>
     </row>
     <row r="638">
@@ -8654,7 +8654,7 @@
         <v>2025</v>
       </c>
       <c r="D638">
-        <v>490.9882717105316</v>
+        <v>490.9882629711722</v>
       </c>
     </row>
     <row r="639">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>501.764231527097</v>
+        <v>521.823584662807</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>514.7873671107917</v>
+        <v>531.5502119219478</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>536.7670706746325</v>
+        <v>556.9273581354887</v>
       </c>
     </row>
     <row r="642">
@@ -8706,7 +8706,7 @@
         <v>2024</v>
       </c>
       <c r="D642">
-        <v>897.2701425601559</v>
+        <v>897.2701425601557</v>
       </c>
     </row>
     <row r="643">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>914.4855410048589</v>
+        <v>952.0355327421746</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>938.6828347872624</v>
+        <v>969.8620239073665</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>979.8250925341903</v>
+        <v>1017.57772095303</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>1316.178123609763</v>
+        <v>1408.186197812403</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>1369.600581912919</v>
+        <v>1438.916016582839</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>1471.129122354892</v>
+        <v>1566.285152669433</v>
       </c>
     </row>
     <row r="652">
@@ -8836,7 +8836,7 @@
         <v>2024</v>
       </c>
       <c r="D652">
-        <v>1444.39637024506</v>
+        <v>1444.396755357935</v>
       </c>
     </row>
     <row r="653">
@@ -8849,7 +8849,7 @@
         <v>2025</v>
       </c>
       <c r="D653">
-        <v>1428.14693032286</v>
+        <v>1428.147404223889</v>
       </c>
     </row>
     <row r="654">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>1481.617163332239</v>
+        <v>1572.309052142143</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>1534.652891886709</v>
+        <v>1603.504600916636</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>1634.230412892419</v>
+        <v>1726.880943842965</v>
       </c>
     </row>
     <row r="657">
@@ -8901,7 +8901,7 @@
         <v>2024</v>
       </c>
       <c r="D657">
-        <v>1222.418805703227</v>
+        <v>1222.418806384912</v>
       </c>
     </row>
     <row r="658">
@@ -8914,7 +8914,7 @@
         <v>2025</v>
       </c>
       <c r="D658">
-        <v>1208.888594870128</v>
+        <v>1208.888592576156</v>
       </c>
     </row>
     <row r="659">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>1255.807078318443</v>
+        <v>1336.113833918444</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>1303.125759422584</v>
+        <v>1364.374844960659</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>1391.478347210988</v>
+        <v>1473.946355755414</v>
       </c>
     </row>
     <row r="662">
@@ -8966,7 +8966,7 @@
         <v>2024</v>
       </c>
       <c r="D662">
-        <v>637.5358568723518</v>
+        <v>637.5358567088546</v>
       </c>
     </row>
     <row r="663">
@@ -8979,7 +8979,7 @@
         <v>2025</v>
       </c>
       <c r="D663">
-        <v>650.1597011993705</v>
+        <v>650.1597009672965</v>
       </c>
     </row>
     <row r="664">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>663.8269317637029</v>
+        <v>703.7852368308862</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>696.6890380186329</v>
+        <v>736.1221751293025</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>741.7395646321311</v>
+        <v>785.3112803627187</v>
       </c>
     </row>
     <row r="667">
@@ -9031,7 +9031,7 @@
         <v>2024</v>
       </c>
       <c r="D667">
-        <v>938.416288858941</v>
+        <v>938.4162888589409</v>
       </c>
     </row>
     <row r="668">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>1036.682852182574</v>
+        <v>1146.2754457959</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>1147.928401586544</v>
+        <v>1272.15293707085</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>1277.853639807071</v>
+        <v>1415.132536554463</v>
       </c>
     </row>
     <row r="672">
@@ -9096,7 +9096,7 @@
         <v>2024</v>
       </c>
       <c r="D672">
-        <v>589.0877557041874</v>
+        <v>589.0877557043771</v>
       </c>
     </row>
     <row r="673">
@@ -9109,7 +9109,7 @@
         <v>2025</v>
       </c>
       <c r="D673">
-        <v>643.6643080554284</v>
+        <v>643.6643080555598</v>
       </c>
     </row>
     <row r="674">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>650.7742135892489</v>
+        <v>719.570577008372</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>720.6081977207303</v>
+        <v>798.5897080989126</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>802.1683100291212</v>
+        <v>888.3446449809709</v>
       </c>
     </row>
     <row r="677">
@@ -9161,7 +9161,7 @@
         <v>2024</v>
       </c>
       <c r="D677">
-        <v>1152.921955136086</v>
+        <v>1152.921955261898</v>
       </c>
     </row>
     <row r="678">
@@ -9174,7 +9174,7 @@
         <v>2025</v>
       </c>
       <c r="D678">
-        <v>1239.488273845755</v>
+        <v>1239.488273828548</v>
       </c>
     </row>
     <row r="679">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>1252.750089009992</v>
+        <v>1365.840038064015</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>1365.839065310707</v>
+        <v>1492.188883981267</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>1497.715052858927</v>
+        <v>1635.116236402893</v>
       </c>
     </row>
     <row r="682">
@@ -9226,7 +9226,7 @@
         <v>2024</v>
       </c>
       <c r="D682">
-        <v>1884.517241168274</v>
+        <v>1884.517241297534</v>
       </c>
     </row>
     <row r="683">
@@ -9239,7 +9239,7 @@
         <v>2025</v>
       </c>
       <c r="D683">
-        <v>2338.446217783129</v>
+        <v>2338.446218106387</v>
       </c>
     </row>
     <row r="684">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>2374.887653135033</v>
+        <v>2901.699501056959</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>2946.922342270468</v>
+        <v>3600.621309573976</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>3656.73689138621</v>
+        <v>4467.889866681723</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>1437.54262115375</v>
+        <v>1655.847418751126</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>1668.025815408106</v>
+        <v>1921.965568357095</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>1936.243716294939</v>
+        <v>2230.918161776597</v>
       </c>
     </row>
     <row r="692">
@@ -9356,7 +9356,7 @@
         <v>2024</v>
       </c>
       <c r="D692">
-        <v>471.0055279552418</v>
+        <v>471.0055279552416</v>
       </c>
     </row>
     <row r="693">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>502.5761819024987</v>
+        <v>545.0022731764839</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>540.9099159089212</v>
+        <v>586.0067299745094</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>590.2905928100087</v>
+        <v>639.862775279033</v>
       </c>
     </row>
     <row r="697">
@@ -9421,7 +9421,7 @@
         <v>2024</v>
       </c>
       <c r="D697">
-        <v>1047.627445544623</v>
+        <v>1047.627444369495</v>
       </c>
     </row>
     <row r="698">
@@ -9434,7 +9434,7 @@
         <v>2025</v>
       </c>
       <c r="D698">
-        <v>1034.065272540782</v>
+        <v>1034.065273243463</v>
       </c>
     </row>
     <row r="699">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>1078.415064330238</v>
+        <v>1153.552473590476</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>1122.055373018922</v>
+        <v>1178.548372475999</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>1204.892945449718</v>
+        <v>1282.577988769001</v>
       </c>
     </row>
     <row r="702">
@@ -9486,7 +9486,7 @@
         <v>2024</v>
       </c>
       <c r="D702">
-        <v>676.8935044127886</v>
+        <v>676.8935044127885</v>
       </c>
     </row>
     <row r="703">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>696.7859455816052</v>
+        <v>745.3337914321362</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>724.9827600597949</v>
+        <v>761.4839478473574</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>778.5058225422945</v>
+        <v>828.6997283473903</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>810.1798409614509</v>
+        <v>866.6282756527962</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>842.9653925108319</v>
+        <v>885.4067630027971</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>905.1987087842102</v>
+        <v>963.5610876970375</v>
       </c>
     </row>
     <row r="712">
@@ -9616,7 +9616,7 @@
         <v>2024</v>
       </c>
       <c r="D712">
-        <v>1104.604990383895</v>
+        <v>1104.604989452266</v>
       </c>
     </row>
     <row r="713">
@@ -9629,7 +9629,7 @@
         <v>2025</v>
       </c>
       <c r="D713">
-        <v>1090.305238476609</v>
+        <v>1090.305240161268</v>
       </c>
     </row>
     <row r="714">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>1137.067072556579</v>
+        <v>1216.290988475396</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>1183.080868639345</v>
+        <v>1242.646381470396</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>1270.423739487205</v>
+        <v>1352.333851999274</v>
       </c>
     </row>
     <row r="717">
@@ -9681,7 +9681,7 @@
         <v>2024</v>
       </c>
       <c r="D717">
-        <v>999.0066050136636</v>
+        <v>999.0066050136633</v>
       </c>
     </row>
     <row r="718">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>1028.365346622154</v>
+        <v>1100.015603845006</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>1069.980277347933</v>
+        <v>1123.851397190999</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>1148.973326238866</v>
+        <v>1223.052977680593</v>
       </c>
     </row>
     <row r="722">
@@ -9746,7 +9746,7 @@
         <v>2024</v>
       </c>
       <c r="D722">
-        <v>876.6947924557952</v>
+        <v>876.694792455795</v>
       </c>
     </row>
     <row r="723">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>902.4590178514321</v>
+        <v>965.3368980772195</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>938.9788605899903</v>
+        <v>986.2543206714696</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>1008.300523773349</v>
+        <v>1073.310352571359</v>
       </c>
     </row>
     <row r="727">
@@ -9811,7 +9811,7 @@
         <v>2024</v>
       </c>
       <c r="D727">
-        <v>1403.927044283899</v>
+        <v>1403.927075971678</v>
       </c>
     </row>
     <row r="728">
@@ -9824,7 +9824,7 @@
         <v>2025</v>
       </c>
       <c r="D728">
-        <v>1385.112945185025</v>
+        <v>1385.112986787733</v>
       </c>
     </row>
     <row r="729">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>1445.110719234099</v>
+        <v>1546.292241778508</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>1503.855098916851</v>
+        <v>1580.16027565102</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>1615.55596221436</v>
+        <v>1720.215661809299</v>
       </c>
     </row>
     <row r="732">
@@ -9876,7 +9876,7 @@
         <v>2024</v>
       </c>
       <c r="D732">
-        <v>1228.542836883599</v>
+        <v>1228.542827488417</v>
       </c>
     </row>
     <row r="733">
@@ -9889,7 +9889,7 @@
         <v>2025</v>
       </c>
       <c r="D733">
-        <v>1212.365835528588</v>
+        <v>1212.365826545939</v>
       </c>
     </row>
     <row r="734">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>1264.614124729883</v>
+        <v>1352.933682095663</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>1315.898301858447</v>
+        <v>1382.395347309695</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>1413.331126586314</v>
+        <v>1504.66427760369</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>1154.626063984992</v>
+        <v>1154.626253954172</v>
       </c>
     </row>
     <row r="738">
@@ -9954,7 +9954,7 @@
         <v>2025</v>
       </c>
       <c r="D738">
-        <v>1124.234157387426</v>
+        <v>1124.23450351771</v>
       </c>
     </row>
     <row r="739">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>1179.845195416629</v>
+        <v>1260.675858494487</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>1219.16073830992</v>
+        <v>1272.573425463205</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>1307.483703229353</v>
+        <v>1389.203945924102</v>
       </c>
     </row>
     <row r="742">
@@ -10006,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D742">
-        <v>864.132088341007</v>
+        <v>864.1320883410071</v>
       </c>
     </row>
     <row r="743">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>887.5483925935388</v>
+        <v>949.0277204782408</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>921.4943986376599</v>
+        <v>965.9701064733702</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>989.0571123209821</v>
+        <v>1052.173510011335</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>1057.517959022622</v>
+        <v>1132.486434109928</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>1102.398325559901</v>
+        <v>1160.450187353566</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>1185.460385107786</v>
+        <v>1263.444533859866</v>
       </c>
     </row>
     <row r="752">
@@ -10136,7 +10136,7 @@
         <v>2024</v>
       </c>
       <c r="D752">
-        <v>997.6906833935016</v>
+        <v>997.6906833935013</v>
       </c>
     </row>
     <row r="753">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>1009.774252219381</v>
+        <v>1075.505088817298</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>1033.821628391459</v>
+        <v>1069.832811909735</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>1104.93983875338</v>
+        <v>1169.481615533108</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>981.257091767372</v>
+        <v>981.2570917673718</v>
       </c>
     </row>
     <row r="758">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>1075.813053015016</v>
+        <v>1180.726859238383</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>1181.30672351209</v>
+        <v>1297.738103258594</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>1303.18635645412</v>
+        <v>1431.094106865384</v>
       </c>
     </row>
     <row r="762">
@@ -10266,7 +10266,7 @@
         <v>2024</v>
       </c>
       <c r="D762">
-        <v>1226.118636079638</v>
+        <v>1226.118273853358</v>
       </c>
     </row>
     <row r="763">
@@ -10279,7 +10279,7 @@
         <v>2025</v>
       </c>
       <c r="D763">
-        <v>1257.976015223879</v>
+        <v>1257.975455183518</v>
       </c>
     </row>
     <row r="764">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>1282.245770498992</v>
+        <v>1362.641751625683</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>1352.669355989707</v>
+        <v>1437.388166536803</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>1445.34807634627</v>
+        <v>1536.010553385603</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>1347.421460572966</v>
+        <v>1347.421451267869</v>
       </c>
     </row>
     <row r="768">
@@ -10344,7 +10344,7 @@
         <v>2025</v>
       </c>
       <c r="D768">
-        <v>1343.695610825742</v>
+        <v>1343.69559760085</v>
       </c>
     </row>
     <row r="769">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>1407.67807307893</v>
+        <v>1531.917124897356</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>1489.641476729191</v>
+        <v>1593.311641311143</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>1630.025658616901</v>
+        <v>1764.848115036334</v>
       </c>
     </row>
     <row r="772">
@@ -10396,7 +10396,7 @@
         <v>2024</v>
       </c>
       <c r="D772">
-        <v>870.2915961861547</v>
+        <v>870.2915961861545</v>
       </c>
     </row>
     <row r="773">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>882.3633534669843</v>
+        <v>941.7057837815687</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>905.0394435051521</v>
+        <v>938.3198663006583</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>969.3362040303408</v>
+        <v>1027.982962008796</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>935.1656833354999</v>
+        <v>995.7691064139492</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>956.7794810320343</v>
+        <v>989.4678765090434</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>1022.306849971758</v>
+        <v>1081.683566992281</v>
       </c>
     </row>
     <row r="782">
@@ -10526,7 +10526,7 @@
         <v>2024</v>
       </c>
       <c r="D782">
-        <v>1081.781391684191</v>
+        <v>1081.781391747137</v>
       </c>
     </row>
     <row r="783">
@@ -10539,7 +10539,7 @@
         <v>2025</v>
       </c>
       <c r="D783">
-        <v>1035.538553119286</v>
+        <v>1035.538552870796</v>
       </c>
     </row>
     <row r="784">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>1094.111927635741</v>
+        <v>1165.015838075084</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>1119.399374678784</v>
+        <v>1157.643732363926</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>1196.064141078425</v>
+        <v>1265.532852109264</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>1018.149666096304</v>
+        <v>1084.130853707665</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>1041.681433003251</v>
+        <v>1077.270531480481</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>1113.023507420221</v>
+        <v>1177.669137072518</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>1212.204519153226</v>
+        <v>1290.761401165449</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>1240.221386721084</v>
+        <v>1282.593671774832</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>1325.16092572822</v>
+        <v>1402.127704244379</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>207.646557772778</v>
+        <v>207.6465573133381</v>
       </c>
     </row>
     <row r="798">
@@ -10734,7 +10734,7 @@
         <v>2025</v>
       </c>
       <c r="D798">
-        <v>198.7701307560829</v>
+        <v>198.7701310336417</v>
       </c>
     </row>
     <row r="799">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>210.0133248848447</v>
+        <v>223.6232855357229</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>214.8671346685618</v>
+        <v>222.2079874881555</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>229.5828700210124</v>
+        <v>242.9173362435273</v>
       </c>
     </row>
     <row r="802">
@@ -10786,7 +10786,7 @@
         <v>2024</v>
       </c>
       <c r="D802">
-        <v>1397.353638693071</v>
+        <v>1397.353487141944</v>
       </c>
     </row>
     <row r="803">
@@ -10799,7 +10799,7 @@
         <v>2025</v>
       </c>
       <c r="D803">
-        <v>1337.621266093791</v>
+        <v>1337.621085478584</v>
       </c>
     </row>
     <row r="804">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>1413.281315773874</v>
+        <v>1504.868706345683</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>1445.945662800526</v>
+        <v>1495.346283288805</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>1544.974802769276</v>
+        <v>1634.708126834121</v>
       </c>
     </row>
     <row r="807">
@@ -10851,7 +10851,7 @@
         <v>2024</v>
       </c>
       <c r="D807">
-        <v>421.6044982804902</v>
+        <v>421.6045542687708</v>
       </c>
     </row>
     <row r="808">
@@ -10864,7 +10864,7 @@
         <v>2025</v>
       </c>
       <c r="D808">
-        <v>403.5819986444091</v>
+        <v>403.5820633653962</v>
       </c>
     </row>
     <row r="809">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>426.4100256505653</v>
+        <v>454.0437031839766</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>436.2652490487296</v>
+        <v>451.1703111450295</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>466.1439744698733</v>
+        <v>493.2183787494916</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>720.4548988016641</v>
+        <v>720.4548988016638</v>
       </c>
     </row>
     <row r="813">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>735.9874516632875</v>
+        <v>789.9808016990044</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>760.9279740575724</v>
+        <v>795.2764659845188</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>819.9754660021071</v>
+        <v>874.6691303227984</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>1712.709249778669</v>
+        <v>1712.709267161721</v>
       </c>
     </row>
     <row r="818">
@@ -10994,7 +10994,7 @@
         <v>2025</v>
       </c>
       <c r="D818">
-        <v>1674.473713813453</v>
+        <v>1674.47373760827</v>
       </c>
     </row>
     <row r="819">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>1762.512364245481</v>
+        <v>1900.354170482227</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>1836.394174710969</v>
+        <v>1934.354734284926</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>1988.789776658258</v>
+        <v>2131.660592109647</v>
       </c>
     </row>
     <row r="822">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>677.6590190736125</v>
+        <v>737.4679748106098</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>717.1162775840018</v>
+        <v>767.0232183084913</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>784.6975018004596</v>
+        <v>849.6013122822777</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>642.7566251034667</v>
+        <v>642.7566250042919</v>
       </c>
     </row>
     <row r="828">
@@ -11124,7 +11124,7 @@
         <v>2025</v>
       </c>
       <c r="D828">
-        <v>694.2602323881546</v>
+        <v>694.2602322306823</v>
       </c>
     </row>
     <row r="829">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>705.9532688941117</v>
+        <v>780.8429489231332</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>778.2196700415271</v>
+        <v>859.5558281713112</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>865.8210730944623</v>
+        <v>957.0644410295322</v>
       </c>
     </row>
     <row r="832">
@@ -11176,7 +11176,7 @@
         <v>2024</v>
       </c>
       <c r="D832">
-        <v>836.7392526120915</v>
+        <v>836.7392526120913</v>
       </c>
     </row>
     <row r="833">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>852.5121070207032</v>
+        <v>886.5935694059602</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>874.6388708834648</v>
+        <v>903.1195442003768</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>911.9830510104202</v>
+        <v>946.236039424924</v>
       </c>
     </row>
     <row r="837">
@@ -11241,7 +11241,7 @@
         <v>2024</v>
       </c>
       <c r="D837">
-        <v>812.2347520803378</v>
+        <v>812.2347520803379</v>
       </c>
     </row>
     <row r="838">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>827.5456862130623</v>
+        <v>860.6290519788204</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>849.0244512806445</v>
+        <v>876.6710472830846</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>885.2749835933042</v>
+        <v>918.5248515180077</v>
       </c>
     </row>
     <row r="842">
@@ -11306,7 +11306,7 @@
         <v>2024</v>
       </c>
       <c r="D842">
-        <v>501.8417760068027</v>
+        <v>501.8417760068025</v>
       </c>
     </row>
     <row r="843">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>527.0013037206069</v>
+        <v>567.2837375922983</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>560.4693323103847</v>
+        <v>602.2458617761364</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>607.7592406835247</v>
+        <v>653.7481226821394</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>340.6747981216388</v>
+        <v>340.674797196083</v>
       </c>
     </row>
     <row r="848">
@@ -11384,7 +11384,7 @@
         <v>2025</v>
       </c>
       <c r="D848">
-        <v>348.1745804844302</v>
+        <v>348.1745825225211</v>
       </c>
     </row>
     <row r="849">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>358.2772937409231</v>
+        <v>385.9825039981091</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>381.5353357919542</v>
+        <v>410.4489281536318</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>414.0998256510005</v>
+        <v>445.8680544415027</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>665.8093334185172</v>
+        <v>717.9146508624013</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>704.7886481185036</v>
+        <v>757.0461104846252</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>766.8687924433674</v>
+        <v>825.6456159830757</v>
       </c>
     </row>
     <row r="857">
@@ -11501,7 +11501,7 @@
         <v>2024</v>
       </c>
       <c r="D857">
-        <v>543.78844209816</v>
+        <v>543.7884422815168</v>
       </c>
     </row>
     <row r="858">
@@ -11514,7 +11514,7 @@
         <v>2025</v>
       </c>
       <c r="D858">
-        <v>541.3843508806171</v>
+        <v>541.384348967049</v>
       </c>
     </row>
     <row r="859">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>563.9933299923582</v>
+        <v>606.8071952552203</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>595.117667620647</v>
+        <v>637.161451206082</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>645.8299343457693</v>
+        <v>693.5211467120015</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>796.0395053752701</v>
+        <v>885.1006317989415</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>880.171430189322</v>
+        <v>977.6916399846056</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>986.343906091683</v>
+        <v>1096.239446491502</v>
       </c>
     </row>
     <row r="867">
@@ -11631,7 +11631,7 @@
         <v>2024</v>
       </c>
       <c r="D867">
-        <v>151.9349953865924</v>
+        <v>151.9349953868134</v>
       </c>
     </row>
     <row r="868">
@@ -11644,7 +11644,7 @@
         <v>2025</v>
       </c>
       <c r="D868">
-        <v>165.4162129469215</v>
+        <v>165.4162129465042</v>
       </c>
     </row>
     <row r="869">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>167.7087586946156</v>
+        <v>185.7750677497482</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>185.9170369766293</v>
+        <v>206.5598302315243</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>207.5827597741273</v>
+        <v>230.4133813378234</v>
       </c>
     </row>
     <row r="872">
@@ -11696,7 +11696,7 @@
         <v>2024</v>
       </c>
       <c r="D872">
-        <v>737.5607422517938</v>
+        <v>737.5607422517937</v>
       </c>
     </row>
     <row r="873">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>809.8011894575817</v>
+        <v>900.610475076519</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>895.659523709763</v>
+        <v>995.1357450083375</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>1003.932053400537</v>
+        <v>1116.049940116756</v>
       </c>
     </row>
     <row r="877">
@@ -11761,7 +11761,7 @@
         <v>2024</v>
       </c>
       <c r="D877">
-        <v>374.5628751863378</v>
+        <v>374.5628751855596</v>
       </c>
     </row>
     <row r="878">
@@ -11774,7 +11774,7 @@
         <v>2025</v>
       </c>
       <c r="D878">
-        <v>407.7979321265876</v>
+        <v>407.7979321272171</v>
       </c>
     </row>
     <row r="879">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>413.4496197610049</v>
+        <v>457.9880519708703</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>458.3380745701058</v>
+        <v>509.2282396154253</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>511.7500189857657</v>
+        <v>568.0337653761853</v>
       </c>
     </row>
     <row r="882">
@@ -11826,7 +11826,7 @@
         <v>2024</v>
       </c>
       <c r="D882">
-        <v>239.0265019482276</v>
+        <v>239.0264900169803</v>
       </c>
     </row>
     <row r="883">
@@ -11839,7 +11839,7 @@
         <v>2025</v>
       </c>
       <c r="D883">
-        <v>259.9732982570285</v>
+        <v>259.9732747698881</v>
       </c>
     </row>
     <row r="884">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>263.6869014853401</v>
+        <v>292.0608658145644</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>292.2198062190692</v>
+        <v>324.6251598769761</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>326.2595022130064</v>
+        <v>362.0923085051133</v>
       </c>
     </row>
     <row r="887">
@@ -11891,7 +11891,7 @@
         <v>2024</v>
       </c>
       <c r="D887">
-        <v>832.1901344050534</v>
+        <v>832.1901344050536</v>
       </c>
     </row>
     <row r="888">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>913.6990813872591</v>
+        <v>1016.15924768884</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>1010.573096215622</v>
+        <v>1122.812178890141</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>1132.737052441656</v>
+        <v>1259.239730745987</v>
       </c>
     </row>
     <row r="892">
@@ -11956,7 +11956,7 @@
         <v>2024</v>
       </c>
       <c r="D892">
-        <v>727.4237813823812</v>
+        <v>727.4237813823811</v>
       </c>
     </row>
     <row r="893">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>797.4047367125427</v>
+        <v>885.9477821824281</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>880.8044465692516</v>
+        <v>977.6229109525082</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>986.3093364417228</v>
+        <v>1095.357316190232</v>
       </c>
     </row>
     <row r="897">
@@ -12021,7 +12021,7 @@
         <v>2024</v>
       </c>
       <c r="D897">
-        <v>948.8767255806924</v>
+        <v>948.8767255806921</v>
       </c>
     </row>
     <row r="898">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>986.9754308277156</v>
+        <v>1064.214748878794</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>1044.757242042322</v>
+        <v>1122.222159224512</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>1136.782945700067</v>
+        <v>1223.911928996896</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>1526.478104364586</v>
+        <v>1645.938123356339</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>1615.844848356891</v>
+        <v>1735.653895161613</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>1758.173831091617</v>
+        <v>1892.9294747569</v>
       </c>
     </row>
     <row r="907">
@@ -12151,7 +12151,7 @@
         <v>2024</v>
       </c>
       <c r="D907">
-        <v>433.8110183421537</v>
+        <v>433.8110183421538</v>
       </c>
     </row>
     <row r="908">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>451.2290518246378</v>
+        <v>486.5416195130713</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>477.645893405077</v>
+        <v>513.0615430834714</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>519.7185490415993</v>
+        <v>559.5524845282554</v>
       </c>
     </row>
     <row r="912">
@@ -12216,7 +12216,7 @@
         <v>2024</v>
       </c>
       <c r="D912">
-        <v>693.8266770704132</v>
+        <v>693.8266751615068</v>
       </c>
     </row>
     <row r="913">
@@ -12229,7 +12229,7 @@
         <v>2025</v>
       </c>
       <c r="D913">
-        <v>693.0647230639886</v>
+        <v>693.0647234012777</v>
       </c>
     </row>
     <row r="914">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>721.6847231928795</v>
+        <v>778.1627679570491</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>763.9352304317691</v>
+        <v>820.5781987993661</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>831.2252020402408</v>
+        <v>894.9346369258293</v>
       </c>
     </row>
     <row r="917">
@@ -12281,7 +12281,7 @@
         <v>2024</v>
       </c>
       <c r="D917">
-        <v>1379.846661826699</v>
+        <v>1379.846659493211</v>
       </c>
     </row>
     <row r="918">
@@ -12294,7 +12294,7 @@
         <v>2025</v>
       </c>
       <c r="D918">
-        <v>1360.902057089012</v>
+        <v>1360.902059963991</v>
       </c>
     </row>
     <row r="919">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>1411.719241131909</v>
+        <v>1494.409003993109</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>1463.048383098801</v>
+        <v>1533.834092196202</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>1556.950186183931</v>
+        <v>1642.607468776147</v>
       </c>
     </row>
     <row r="922">
@@ -12346,7 +12346,7 @@
         <v>2024</v>
       </c>
       <c r="D922">
-        <v>462.7016487388981</v>
+        <v>462.701648738898</v>
       </c>
     </row>
     <row r="923">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>481.2796824333453</v>
+        <v>518.943970141336</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>509.4558192221045</v>
+        <v>547.2300591051758</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>554.3303989307016</v>
+        <v>596.8171675455931</v>
       </c>
     </row>
     <row r="927">
@@ -12411,7 +12411,7 @@
         <v>2024</v>
       </c>
       <c r="D927">
-        <v>822.1012258350993</v>
+        <v>822.1012258350988</v>
       </c>
     </row>
     <row r="928">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>855.0673934115388</v>
+        <v>921.9658979216684</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>905.0768881586064</v>
+        <v>972.129710076302</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>984.7683763897707</v>
+        <v>1060.209521171341</v>
       </c>
     </row>
     <row r="932">
@@ -12476,7 +12476,7 @@
         <v>2024</v>
       </c>
       <c r="D932">
-        <v>732.4082017107911</v>
+        <v>732.4082017107909</v>
       </c>
     </row>
     <row r="933">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>761.1517854836175</v>
+        <v>820.4624760829993</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>805.0465699421093</v>
+        <v>864.0925550862663</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>875.6049243879997</v>
+        <v>942.2597419947333</v>
       </c>
     </row>
     <row r="937">
@@ -12541,7 +12541,7 @@
         <v>2024</v>
       </c>
       <c r="D937">
-        <v>588.6467355874328</v>
+        <v>588.6467355874327</v>
       </c>
     </row>
     <row r="938">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>612.2816490311637</v>
+        <v>660.1979657488479</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>648.1272165319389</v>
+        <v>696.1834380897585</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>705.2164338916682</v>
+        <v>759.2678978363981</v>
       </c>
     </row>
     <row r="942">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>949.5383430236657</v>
+        <v>1102.732394127907</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>1107.3584191064</v>
+        <v>1290.966656473497</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>1304.042945619329</v>
+        <v>1518.429786256582</v>
       </c>
     </row>
     <row r="947">
@@ -12671,7 +12671,7 @@
         <v>2024</v>
       </c>
       <c r="D947">
-        <v>1375.306008989128</v>
+        <v>1375.306008713878</v>
       </c>
     </row>
     <row r="948">
@@ -12684,7 +12684,7 @@
         <v>2025</v>
       </c>
       <c r="D948">
-        <v>1327.444595692261</v>
+        <v>1327.444596187424</v>
       </c>
     </row>
     <row r="949">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>1404.828225282374</v>
+        <v>1511.734071060096</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>1455.406220224645</v>
+        <v>1527.039994661952</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>1573.797039985058</v>
+        <v>1682.617055251372</v>
       </c>
     </row>
     <row r="952">
@@ -12736,7 +12736,7 @@
         <v>2024</v>
       </c>
       <c r="D952">
-        <v>737.3430023947676</v>
+        <v>737.3425466494292</v>
       </c>
     </row>
     <row r="953">
@@ -12749,7 +12749,7 @@
         <v>2025</v>
       </c>
       <c r="D953">
-        <v>807.3106930102847</v>
+        <v>807.3099056871564</v>
       </c>
     </row>
     <row r="954">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>831.4487706157242</v>
+        <v>949.6912465560251</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>946.6157896168537</v>
+        <v>1082.84204174948</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>1094.694561785594</v>
+        <v>1251.544126400976</v>
       </c>
     </row>
     <row r="957">
@@ -12801,7 +12801,7 @@
         <v>2024</v>
       </c>
       <c r="D957">
-        <v>536.9635721246574</v>
+        <v>536.9635721246221</v>
       </c>
     </row>
     <row r="958">
@@ -12814,7 +12814,7 @@
         <v>2025</v>
       </c>
       <c r="D958">
-        <v>610.2691820858162</v>
+        <v>610.2691820858064</v>
       </c>
     </row>
     <row r="959">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>624.1013904480828</v>
+        <v>725.0714171337519</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>728.2057736543193</v>
+        <v>849.2767217433513</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>857.8899390470688</v>
+        <v>999.3216782640482</v>
       </c>
     </row>
     <row r="962">
@@ -12866,7 +12866,7 @@
         <v>2024</v>
       </c>
       <c r="D962">
-        <v>926.3946491934167</v>
+        <v>926.3946491934169</v>
       </c>
     </row>
     <row r="963">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>1017.295520229441</v>
+        <v>1125.083348375443</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>1121.261412517438</v>
+        <v>1238.292326057407</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>1247.328663001086</v>
+        <v>1378.610314570409</v>
       </c>
     </row>
     <row r="967">
@@ -12931,7 +12931,7 @@
         <v>2024</v>
       </c>
       <c r="D967">
-        <v>571.0153132866343</v>
+        <v>571.0153132866342</v>
       </c>
     </row>
     <row r="968">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>595.8835725338985</v>
+        <v>637.6362571428801</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>628.8064882117877</v>
+        <v>669.784060320302</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>676.7590353526419</v>
+        <v>722.8567885947436</v>
       </c>
     </row>
     <row r="972">
@@ -12996,7 +12996,7 @@
         <v>2024</v>
       </c>
       <c r="D972">
-        <v>895.767163337905</v>
+        <v>895.7671633379048</v>
       </c>
     </row>
     <row r="973">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>983.8401842177769</v>
+        <v>1088.20897152233</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>1084.553121621549</v>
+        <v>1197.905975549221</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>1206.637404623775</v>
+        <v>1333.797266799774</v>
       </c>
     </row>
     <row r="977">
@@ -13061,7 +13061,7 @@
         <v>2024</v>
       </c>
       <c r="D977">
-        <v>50.25422159129118</v>
+        <v>50.25422128526945</v>
       </c>
     </row>
     <row r="978">
@@ -13074,7 +13074,7 @@
         <v>2025</v>
       </c>
       <c r="D978">
-        <v>51.30865403455277</v>
+        <v>51.3086535874093</v>
       </c>
     </row>
     <row r="979">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>52.73521727413902</v>
+        <v>56.64277544261671</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>55.91708176852296</v>
+        <v>59.79981407066313</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>60.40270540311028</v>
+        <v>64.76552358482644</v>
       </c>
     </row>
     <row r="982">
@@ -13126,7 +13126,7 @@
         <v>2024</v>
       </c>
       <c r="D982">
-        <v>430.666913577968</v>
+        <v>430.6669138134282</v>
       </c>
     </row>
     <row r="983">
@@ -13139,7 +13139,7 @@
         <v>2025</v>
       </c>
       <c r="D983">
-        <v>465.1758725447039</v>
+        <v>465.1758725303008</v>
       </c>
     </row>
     <row r="984">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>473.0105930394657</v>
+        <v>523.1889932215722</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>521.4312921026539</v>
+        <v>575.9290108287753</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>580.1269334531547</v>
+        <v>641.2627968043571</v>
       </c>
     </row>
     <row r="987">
@@ -13191,7 +13191,7 @@
         <v>2024</v>
       </c>
       <c r="D987">
-        <v>652.7373191431966</v>
+        <v>652.737316688035</v>
       </c>
     </row>
     <row r="988">
@@ -13204,7 +13204,7 @@
         <v>2025</v>
       </c>
       <c r="D988">
-        <v>705.0406774233372</v>
+        <v>705.0406743475925</v>
       </c>
     </row>
     <row r="989">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>716.9152814694521</v>
+        <v>792.9678420851144</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>790.3038361997495</v>
+        <v>872.9029758189992</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>879.2655134758451</v>
+        <v>971.9256986039842</v>
       </c>
     </row>
     <row r="992">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>1144.981722588301</v>
+        <v>1266.444910581369</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>1262.190297606429</v>
+        <v>1394.109059573141</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>1404.270580666885</v>
+        <v>1552.257771846147</v>
       </c>
     </row>
     <row r="997">
@@ -13321,7 +13321,7 @@
         <v>2024</v>
       </c>
       <c r="D997">
-        <v>962.9453918886244</v>
+        <v>962.9453918886246</v>
       </c>
     </row>
     <row r="998">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>1115.522056382502</v>
+        <v>1283.636292412838</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>1290.463087413479</v>
+        <v>1487.768484981558</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>1499.843243563489</v>
+        <v>1728.124953296072</v>
       </c>
     </row>
     <row r="1002">
@@ -13386,7 +13386,7 @@
         <v>2024</v>
       </c>
       <c r="D1002">
-        <v>400.8336627735732</v>
+        <v>400.8336621143558</v>
       </c>
     </row>
     <row r="1003">
@@ -13399,7 +13399,7 @@
         <v>2025</v>
       </c>
       <c r="D1003">
-        <v>457.877183426517</v>
+        <v>457.8771835223263</v>
       </c>
     </row>
     <row r="1004">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>464.3448455711939</v>
+        <v>534.3236905110199</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>537.1653787000629</v>
+        <v>619.2952626219811</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>624.3214783206314</v>
+        <v>719.3454830729947</v>
       </c>
     </row>
     <row r="1007">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>1426.159532600434</v>
+        <v>1640.628388669605</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>1649.240946733062</v>
+        <v>1900.871145536699</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>1916.2695858769</v>
+        <v>2207.309223424396</v>
       </c>
     </row>
     <row r="1012">
@@ -13516,7 +13516,7 @@
         <v>2024</v>
       </c>
       <c r="D1012">
-        <v>597.450067682565</v>
+        <v>597.4500676474214</v>
       </c>
     </row>
     <row r="1013">
@@ -13529,7 +13529,7 @@
         <v>2025</v>
       </c>
       <c r="D1013">
-        <v>603.9655558749212</v>
+        <v>603.965555777864</v>
       </c>
     </row>
     <row r="1014">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>632.5911975719662</v>
+        <v>696.3579690206313</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>682.4913995333177</v>
+        <v>747.1506733477438</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>759.1130649748335</v>
+        <v>833.8305519126123</v>
       </c>
     </row>
     <row r="1017">
@@ -13581,7 +13581,7 @@
         <v>2024</v>
       </c>
       <c r="D1017">
-        <v>384.1254323041369</v>
+        <v>384.1254324031258</v>
       </c>
     </row>
     <row r="1018">
@@ -13594,7 +13594,7 @@
         <v>2025</v>
       </c>
       <c r="D1018">
-        <v>376.6982882404821</v>
+        <v>376.6982882250869</v>
       </c>
     </row>
     <row r="1019">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>410.1722462648665</v>
+        <v>469.6930183697795</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>450.1458096135463</v>
+        <v>504.0461223629121</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>522.6039828829933</v>
+        <v>594.0728081797153</v>
       </c>
     </row>
     <row r="1022">
@@ -13646,7 +13646,7 @@
         <v>2024</v>
       </c>
       <c r="D1022">
-        <v>474.3672807943745</v>
+        <v>474.3672807944063</v>
       </c>
     </row>
     <row r="1023">
@@ -13659,7 +13659,7 @@
         <v>2025</v>
       </c>
       <c r="D1023">
-        <v>468.8032337010594</v>
+        <v>468.8032337010669</v>
       </c>
     </row>
     <row r="1024">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>494.7084670600482</v>
+        <v>540.9548866847504</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>528.3956873707483</v>
+        <v>575.4289417265021</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>585.0692029421588</v>
+        <v>638.823780415341</v>
       </c>
     </row>
     <row r="1027">
@@ -13711,7 +13711,7 @@
         <v>2024</v>
       </c>
       <c r="D1027">
-        <v>506.6423666180727</v>
+        <v>506.6423667183957</v>
       </c>
     </row>
     <row r="1028">
@@ -13724,7 +13724,7 @@
         <v>2025</v>
       </c>
       <c r="D1028">
-        <v>501.3659200979334</v>
+        <v>501.3659198952376</v>
       </c>
     </row>
     <row r="1029">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>545.9759131556411</v>
+        <v>629.9194526841801</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>605.2387266873149</v>
+        <v>684.4308067974127</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>708.9109901979165</v>
+        <v>812.3827102487758</v>
       </c>
     </row>
     <row r="1032">
@@ -13776,7 +13776,7 @@
         <v>2024</v>
       </c>
       <c r="D1032">
-        <v>3.786868349675082</v>
+        <v>3.78687040792681</v>
       </c>
     </row>
     <row r="1033">
@@ -13789,7 +13789,7 @@
         <v>2025</v>
       </c>
       <c r="D1033">
-        <v>3.62498014544105</v>
+        <v>3.624982589253674</v>
       </c>
     </row>
     <row r="1034">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>3.830027568976325</v>
+        <v>4.078238772908941</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>3.91854221813051</v>
+        <v>4.052417664477382</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>4.186914149628721</v>
+        <v>4.43010352159639</v>
       </c>
     </row>
     <row r="1037">
@@ -13841,7 +13841,7 @@
         <v>2024</v>
       </c>
       <c r="D1037">
-        <v>344.8536810294504</v>
+        <v>344.8536810294503</v>
       </c>
     </row>
     <row r="1038">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>369.3565732487307</v>
+        <v>422.0020640590967</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>406.7415126144782</v>
+        <v>457.0084991266928</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>471.5478592474093</v>
+        <v>535.6330145564385</v>
       </c>
     </row>
     <row r="1042">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>394.2216142640739</v>
+        <v>431.1088773360926</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>421.1445239742469</v>
+        <v>458.7124756252085</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>466.365633606415</v>
+        <v>509.2755478579439</v>
       </c>
     </row>
     <row r="1047">
@@ -13971,7 +13971,7 @@
         <v>2024</v>
       </c>
       <c r="D1047">
-        <v>577.1422593535189</v>
+        <v>577.1422593535187</v>
       </c>
     </row>
     <row r="1048">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>601.9995630470634</v>
+        <v>658.3285712924799</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>643.1124621810583</v>
+        <v>700.4809567555034</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>712.1677469538313</v>
+        <v>777.6937128135107</v>
       </c>
     </row>
     <row r="1052">
@@ -14036,7 +14036,7 @@
         <v>2024</v>
       </c>
       <c r="D1052">
-        <v>671.8414033893711</v>
+        <v>671.8414033892325</v>
       </c>
     </row>
     <row r="1053">
@@ -14049,7 +14049,7 @@
         <v>2025</v>
       </c>
       <c r="D1053">
-        <v>685.6605694752063</v>
+        <v>685.6605694751357</v>
       </c>
     </row>
     <row r="1054">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>715.2925068299654</v>
+        <v>788.3755476251177</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>776.1466204394914</v>
+        <v>854.4037442177521</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>865.4423661401712</v>
+        <v>953.5478065769437</v>
       </c>
     </row>
     <row r="1057">
@@ -14101,7 +14101,7 @@
         <v>2024</v>
       </c>
       <c r="D1057">
-        <v>792.8340567387107</v>
+        <v>792.8340567387105</v>
       </c>
     </row>
     <row r="1058">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>859.4664901588544</v>
+        <v>954.4286782837531</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>945.3147345448057</v>
+        <v>1050.378789896565</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>1061.31628832923</v>
+        <v>1179.141396807373</v>
       </c>
     </row>
     <row r="1062">
@@ -14166,7 +14166,7 @@
         <v>2024</v>
       </c>
       <c r="D1062">
-        <v>389.8008016779817</v>
+        <v>389.8008019352083</v>
       </c>
     </row>
     <row r="1063">
@@ -14179,7 +14179,7 @@
         <v>2025</v>
       </c>
       <c r="D1063">
-        <v>385.3333877401546</v>
+        <v>385.3333877347804</v>
       </c>
     </row>
     <row r="1064">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>406.5893496887549</v>
+        <v>444.6338598834246</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>434.3569012709415</v>
+        <v>473.103456501623</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>480.9967119285201</v>
+        <v>525.2528199312272</v>
       </c>
     </row>
     <row r="1067">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>806.2417604456663</v>
+        <v>899.9641336706715</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>873.876901129507</v>
+        <v>966.3557035792433</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>988.7240795020334</v>
+        <v>1099.852401256186</v>
       </c>
     </row>
     <row r="1072">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>1518.092253655708</v>
+        <v>1751.498068048791</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>1682.873456456696</v>
+        <v>1903.068218789781</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>1971.13527116659</v>
+        <v>2258.839526661198</v>
       </c>
     </row>
     <row r="1077">
@@ -14361,7 +14361,7 @@
         <v>2024</v>
       </c>
       <c r="D1077">
-        <v>569.8446868343202</v>
+        <v>569.8446868340792</v>
       </c>
     </row>
     <row r="1078">
@@ -14374,7 +14374,7 @@
         <v>2025</v>
       </c>
       <c r="D1078">
-        <v>587.8256810044738</v>
+        <v>587.8256810043699</v>
       </c>
     </row>
     <row r="1079">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>611.0188920406504</v>
+        <v>675.3863082828329</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>666.5562080920168</v>
+        <v>736.4566349881189</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>745.1742027396775</v>
+        <v>823.6796649469843</v>
       </c>
     </row>
     <row r="1082">
@@ -14426,7 +14426,7 @@
         <v>2024</v>
       </c>
       <c r="D1082">
-        <v>466.8716573626452</v>
+        <v>466.8716573624559</v>
       </c>
     </row>
     <row r="1083">
@@ -14439,7 +14439,7 @@
         <v>2025</v>
       </c>
       <c r="D1083">
-        <v>461.5209856195864</v>
+        <v>461.5209856195282</v>
       </c>
     </row>
     <row r="1084">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>486.979628579059</v>
+        <v>532.5462427547046</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>520.2373535650108</v>
+        <v>566.6448323203124</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>576.0987204255824</v>
+        <v>629.1050862009782</v>
       </c>
     </row>
     <row r="1087">
@@ -14491,7 +14491,7 @@
         <v>2024</v>
       </c>
       <c r="D1087">
-        <v>517.8569905584858</v>
+        <v>517.8569905582767</v>
       </c>
     </row>
     <row r="1088">
@@ -14504,7 +14504,7 @@
         <v>2025</v>
       </c>
       <c r="D1088">
-        <v>511.9220125784634</v>
+        <v>511.9220125784042</v>
       </c>
     </row>
     <row r="1089">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>540.1608891084703</v>
+        <v>590.7036641882008</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>577.0505758947326</v>
+        <v>628.5260509170756</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>639.0123565883333</v>
+        <v>697.8073546589211</v>
       </c>
     </row>
     <row r="1092">
@@ -14556,7 +14556,7 @@
         <v>2024</v>
       </c>
       <c r="D1092">
-        <v>825.0342792798266</v>
+        <v>825.034279279826</v>
       </c>
     </row>
     <row r="1093">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>902.145522392264</v>
+        <v>1005.723747125025</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>998.710699276923</v>
+        <v>1114.729809933804</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>1125.322377614609</v>
+        <v>1255.513575784998</v>
       </c>
     </row>
     <row r="1097">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>961.6151206917804</v>
+        <v>1086.554847337519</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>1086.313636402852</v>
+        <v>1230.153613452821</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>1239.860268884602</v>
+        <v>1402.872345863464</v>
       </c>
     </row>
     <row r="1102">
@@ -14686,7 +14686,7 @@
         <v>2024</v>
       </c>
       <c r="D1102">
-        <v>324.2905712167758</v>
+        <v>324.2905712167586</v>
       </c>
     </row>
     <row r="1103">
@@ -14699,7 +14699,7 @@
         <v>2025</v>
       </c>
       <c r="D1103">
-        <v>320.5739306434623</v>
+        <v>320.5739306434769</v>
       </c>
     </row>
     <row r="1104">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>338.2576113806904</v>
+        <v>369.9083322818324</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>361.3585170322572</v>
+        <v>393.5932881715007</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>400.1600045717315</v>
+        <v>436.9783932619071</v>
       </c>
     </row>
     <row r="1107">
@@ -14751,7 +14751,7 @@
         <v>2024</v>
       </c>
       <c r="D1107">
-        <v>588.1100340921963</v>
+        <v>588.1100340921964</v>
       </c>
     </row>
     <row r="1108">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>613.4397177703189</v>
+        <v>670.8391791758874</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>655.3339112236409</v>
+        <v>713.7926144521626</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>725.701494283347</v>
+        <v>792.4726892219905</v>
       </c>
     </row>
     <row r="1112">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>1091.44371575237</v>
+        <v>1217.317424163657</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>1182.331579939171</v>
+        <v>1306.688557944757</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>1336.565692584875</v>
+        <v>1485.691095646213</v>
       </c>
     </row>
     <row r="1117">
@@ -14881,7 +14881,7 @@
         <v>2024</v>
       </c>
       <c r="D1117">
-        <v>615.6519473835095</v>
+        <v>615.6519473835094</v>
       </c>
     </row>
     <row r="1118">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>642.4298723851938</v>
+        <v>702.6475508163146</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>686.5183798895843</v>
+        <v>747.917469896681</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>760.3332296674821</v>
+        <v>830.4346682894507</v>
       </c>
     </row>
     <row r="1122">
@@ -14946,7 +14946,7 @@
         <v>2024</v>
       </c>
       <c r="D1122">
-        <v>382.9513555131054</v>
+        <v>382.951355513116</v>
       </c>
     </row>
     <row r="1123">
@@ -14959,7 +14959,7 @@
         <v>2025</v>
       </c>
       <c r="D1123">
-        <v>437.4500011780399</v>
+        <v>437.4500011780621</v>
       </c>
     </row>
     <row r="1124">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>443.6291241209958</v>
+        <v>510.48601567188</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>513.2009272514225</v>
+        <v>591.6667649044434</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>596.4687476527555</v>
+        <v>687.2534623821227</v>
       </c>
     </row>
     <row r="1127">
@@ -15011,7 +15011,7 @@
         <v>2024</v>
       </c>
       <c r="D1127">
-        <v>1176.614178430625</v>
+        <v>1176.614178430624</v>
       </c>
     </row>
     <row r="1128">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>1199.288950732307</v>
+        <v>1301.101204991208</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>1242.110876281618</v>
+        <v>1305.079955078559</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>1354.93568914498</v>
+        <v>1458.625907365172</v>
       </c>
     </row>
     <row r="1132">
@@ -15076,7 +15076,7 @@
         <v>2024</v>
       </c>
       <c r="D1132">
-        <v>746.8094457784961</v>
+        <v>746.809447081543</v>
       </c>
     </row>
     <row r="1133">
@@ -15089,7 +15089,7 @@
         <v>2025</v>
       </c>
       <c r="D1133">
-        <v>723.4893154854553</v>
+        <v>723.489315915437</v>
       </c>
     </row>
     <row r="1134">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>783.1500166054111</v>
+        <v>879.1512907613309</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>840.708222920032</v>
+        <v>919.4840662272301</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>953.5718937219643</v>
+        <v>1062.080331200245</v>
       </c>
     </row>
     <row r="1137">
@@ -15141,7 +15141,7 @@
         <v>2024</v>
       </c>
       <c r="D1137">
-        <v>1107.224372623312</v>
+        <v>1107.223642945436</v>
       </c>
     </row>
     <row r="1138">
@@ -15154,7 +15154,7 @@
         <v>2025</v>
       </c>
       <c r="D1138">
-        <v>1249.430935517977</v>
+        <v>1249.429390820779</v>
       </c>
     </row>
     <row r="1139">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>1279.516701470826</v>
+        <v>1481.892139263651</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>1486.472525123037</v>
+        <v>1728.087742589255</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>1745.606395407924</v>
+        <v>2026.826588108114</v>
       </c>
     </row>
     <row r="1142">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>1217.080874962034</v>
+        <v>1413.98507269778</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>1420.097456740105</v>
+        <v>1656.20084852072</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>1672.997600895173</v>
+        <v>1948.806881467018</v>
       </c>
     </row>
     <row r="1147">
@@ -15271,7 +15271,7 @@
         <v>2024</v>
       </c>
       <c r="D1147">
-        <v>374.4808361955018</v>
+        <v>374.4808361955017</v>
       </c>
     </row>
     <row r="1148">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>435.251094971379</v>
+        <v>505.6680324843891</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>507.8539258828259</v>
+        <v>592.2893289298424</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>598.2962328254335</v>
+        <v>696.9313370620694</v>
       </c>
     </row>
     <row r="1152">
@@ -15336,7 +15336,7 @@
         <v>2024</v>
       </c>
       <c r="D1152">
-        <v>1261.618900220877</v>
+        <v>1261.618900007295</v>
       </c>
     </row>
     <row r="1153">
@@ -15349,7 +15349,7 @@
         <v>2025</v>
       </c>
       <c r="D1153">
-        <v>1248.480272097589</v>
+        <v>1248.480272500064</v>
       </c>
     </row>
     <row r="1154">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>1359.565827162823</v>
+        <v>1568.598309283502</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>1507.139765194022</v>
+        <v>1704.340715132934</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>1765.299916939301</v>
+        <v>2022.960728065892</v>
       </c>
     </row>
     <row r="1157">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>565.2721489552561</v>
+        <v>656.7244877670523</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>659.563382318975</v>
+        <v>769.2218748095689</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>777.0231907976495</v>
+        <v>905.1232098163273</v>
       </c>
     </row>
     <row r="1162">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>1086.547568739004</v>
+        <v>1253.630876749475</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>1204.679131069928</v>
+        <v>1362.461444112139</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>1411.062212846157</v>
+        <v>1617.094317676858</v>
       </c>
     </row>
     <row r="1167">
@@ -15531,7 +15531,7 @@
         <v>2024</v>
       </c>
       <c r="D1167">
-        <v>1486.516102388485</v>
+        <v>1486.516102388484</v>
       </c>
     </row>
     <row r="1168">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>1601.923176373983</v>
+        <v>1848.217938497813</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>1775.80381514183</v>
+        <v>2008.158018692023</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>2079.98379666048</v>
+        <v>2383.575432791606</v>
       </c>
     </row>
     <row r="1172">
@@ -15596,7 +15596,7 @@
         <v>2024</v>
       </c>
       <c r="D1172">
-        <v>520.1062832630405</v>
+        <v>520.1062832630404</v>
       </c>
     </row>
     <row r="1173">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>560.4851133872357</v>
+        <v>646.6594341863547</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>621.3228268151657</v>
+        <v>702.6194235468304</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>727.7501589365575</v>
+        <v>833.9716190764872</v>
       </c>
     </row>
     <row r="1177">
@@ -15661,7 +15661,7 @@
         <v>2024</v>
       </c>
       <c r="D1177">
-        <v>939.4823078109101</v>
+        <v>939.4823077590192</v>
       </c>
     </row>
     <row r="1178">
@@ -15674,7 +15674,7 @@
         <v>2025</v>
       </c>
       <c r="D1178">
-        <v>929.6983104849788</v>
+        <v>929.698310327229</v>
       </c>
     </row>
     <row r="1179">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>1012.419812721225</v>
+        <v>1168.078819643968</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>1122.312768313031</v>
+        <v>1269.161174200239</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>1314.555374364797</v>
+        <v>1506.426128127001</v>
       </c>
     </row>
     <row r="1182">
@@ -15726,7 +15726,7 @@
         <v>2024</v>
       </c>
       <c r="D1182">
-        <v>818.4799367842784</v>
+        <v>818.4799367842785</v>
       </c>
     </row>
     <row r="1183">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>883.4309915016923</v>
+        <v>949.558882212785</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>951.4504481673872</v>
+        <v>1022.538306781363</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>1024.340249510846</v>
+        <v>1100.92355953839</v>
       </c>
     </row>
     <row r="1187">
@@ -15791,7 +15791,7 @@
         <v>2024</v>
       </c>
       <c r="D1187">
-        <v>244.1594114468755</v>
+        <v>244.1594114350619</v>
       </c>
     </row>
     <row r="1188">
@@ -15804,7 +15804,7 @@
         <v>2025</v>
       </c>
       <c r="D1188">
-        <v>249.5344133045074</v>
+        <v>249.5344132984268</v>
       </c>
     </row>
     <row r="1189">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>256.7749828143232</v>
+        <v>276.6311236744903</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>273.4438509658443</v>
+        <v>294.1660158851739</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>296.7826047563719</v>
+        <v>319.5506746512705</v>
       </c>
     </row>
     <row r="1192">
@@ -15856,7 +15856,7 @@
         <v>2024</v>
       </c>
       <c r="D1192">
-        <v>128.7101387807248</v>
+        <v>128.7101387001823</v>
       </c>
     </row>
     <row r="1193">
@@ -15869,7 +15869,7 @@
         <v>2025</v>
       </c>
       <c r="D1193">
-        <v>131.5665529124592</v>
+        <v>131.5665531196768</v>
       </c>
     </row>
     <row r="1194">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>135.3742005780031</v>
+        <v>145.8459101938848</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>144.1742551871017</v>
+        <v>155.1103030070646</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>156.4840992182266</v>
+        <v>168.4960854630767</v>
       </c>
     </row>
     <row r="1197">
@@ -15921,7 +15921,7 @@
         <v>2024</v>
       </c>
       <c r="D1197">
-        <v>921.1089318987431</v>
+        <v>921.1089318993095</v>
       </c>
     </row>
     <row r="1198">
@@ -15934,7 +15934,7 @@
         <v>2025</v>
       </c>
       <c r="D1198">
-        <v>931.5735113877162</v>
+        <v>931.5735113885412</v>
       </c>
     </row>
     <row r="1199">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>949.5520638960884</v>
+        <v>995.9737484031444</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>988.4496872757517</v>
+        <v>1037.801802039501</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>1042.701138334656</v>
+        <v>1094.327864566744</v>
       </c>
     </row>
     <row r="1202">
@@ -15986,7 +15986,7 @@
         <v>2024</v>
       </c>
       <c r="D1202">
-        <v>0.3854103528180163</v>
+        <v>0.3854103528180831</v>
       </c>
     </row>
     <row r="1203">
@@ -15999,7 +15999,7 @@
         <v>2025</v>
       </c>
       <c r="D1203">
-        <v>0.3907609764748024</v>
+        <v>0.3907609764748937</v>
       </c>
     </row>
     <row r="1204">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>0.4021644931906247</v>
+        <v>0.4303221502792134</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>0.424356416596625</v>
+        <v>0.4519861230362224</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>0.4566956511350034</v>
+        <v>0.4877786800902155</v>
       </c>
     </row>
     <row r="1207">
@@ -16051,7 +16051,7 @@
         <v>2024</v>
       </c>
       <c r="D1207">
-        <v>881.9532823285873</v>
+        <v>881.9532823285872</v>
       </c>
     </row>
     <row r="1208">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>937.2024984566888</v>
+        <v>1014.82516141383</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>1004.45778847213</v>
+        <v>1083.71915237491</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>1093.688430396907</v>
+        <v>1182.52097740198</v>
       </c>
     </row>
     <row r="1212">
@@ -16116,7 +16116,7 @@
         <v>2024</v>
       </c>
       <c r="D1212">
-        <v>851.0841608167494</v>
+        <v>851.0841608167489</v>
       </c>
     </row>
     <row r="1213">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>940.2056941238328</v>
+        <v>1039.599228748237</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>1041.098349462318</v>
+        <v>1153.762126832205</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>1158.932304768095</v>
+        <v>1283.435558723845</v>
       </c>
     </row>
     <row r="1217">
@@ -16181,7 +16181,7 @@
         <v>2024</v>
       </c>
       <c r="D1217">
-        <v>827.975599640796</v>
+        <v>827.9755996407957</v>
       </c>
     </row>
     <row r="1218">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>917.5298839527183</v>
+        <v>1018.933374892278</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>1019.536026157568</v>
+        <v>1133.994026255345</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>1140.084959352144</v>
+        <v>1267.327476908808</v>
       </c>
     </row>
     <row r="1222">
@@ -16246,7 +16246,7 @@
         <v>2024</v>
       </c>
       <c r="D1222">
-        <v>2241.119994085746</v>
+        <v>2241.11999408581</v>
       </c>
     </row>
     <row r="1223">
@@ -16259,7 +16259,7 @@
         <v>2025</v>
       </c>
       <c r="D1223">
-        <v>2717.364169748702</v>
+        <v>2717.364169748857</v>
       </c>
     </row>
     <row r="1224">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>2751.102335051729</v>
+        <v>3294.822841321014</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>3335.727413188311</v>
+        <v>3994.995228495937</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>4044.592370512903</v>
+        <v>4843.959041723151</v>
       </c>
     </row>
   </sheetData>
